--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -38,6 +38,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="19 Persistent HP MP" sheetId="29" state="visible" r:id="rId29"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20 Item Affix Names" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Unit Progression" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22 Economy Framework" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23 Materials System" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Project Identity'!$A$1:$D$79</definedName>
@@ -56,7 +58,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +81,18 @@
     <font>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="002F5496"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +117,12 @@
         <bgColor rgb="00D9E2F3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -124,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -136,6 +154,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -503,7 +530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2640,6 +2667,40 @@
       <c r="C105" t="inlineStr">
         <is>
           <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>RNG scope</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>No hit/miss, dodge, or debuff infliction RNG. Combat resolution is deterministic. RNG is used for procedural generation: maps, item bonuses, loot drops, enemy spawns, recruit pools, terrain placement.</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Equipment Downgrade</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Downgrading equipment is FREE. No compensation. Purpose: reduce item level for lower-level unit equip. Upgrading costs gold/materials (blacksmith design pending).</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
         </is>
       </c>
     </row>
@@ -42061,7 +42122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42074,7 +42135,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kill-based XP + procedural objectives. Linear ramp: XP to level = 500 + (Level × 20). L99 cap at launch. Evolutions post-launch.</t>
+          <t>Kill-based XP + procedural objectives. Linear ramp: XP to level = 500 + (Level × 20). Defeat/victory reward rules. Dispatch. Bench rate 65%.</t>
         </is>
       </c>
     </row>
@@ -42553,12 +42614,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>50% of battle XP. Prevents permanent roster gaps.</t>
+          <t>65% of battle XP. Prevents permanent roster gaps. Benched units stay viable without mandatory rotation.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Locked — updated from 50% based on simulation v2</t>
         </is>
       </c>
     </row>
@@ -43103,12 +43164,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dispatched units earn flat XP based on dispatch difficulty × duration. Unit unavailable for N battles.</t>
+          <t>Dispatched units earn flat XP based on dispatch difficulty × duration. Unit unavailable for N battles. Dispatch appears as a quest on the quest board but does NOT initiate a battle. Player selects units and sends them; they return after the specified duration with rewards.</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Locked direction</t>
+          <t>Locked direction — dispatch is quest board activity, not battle</t>
         </is>
       </c>
     </row>
@@ -43172,7 +43233,6 @@
           <t>Slice 6 owns XP system implementation. Base formula can work without Slice 5. Procedural objectives need Slice 5 map spawns.</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -43190,7 +43250,6 @@
           <t>Slice 5: procedural maps for objectives. Slice 8: quest board, dispatch, exploration. Daily/seasonal events: separate reward systems, may grant XP as part of reward.</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -43365,6 +43424,2136 @@
       <c r="D62" t="inlineStr">
         <is>
           <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Defeat Rewards</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Enemy kill XP</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>XP from enemies defeated during battle is retained even on wipeout. Per-kill XP accumulates during battle and is awarded regardless of outcome.</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Defeat Rewards</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Enemy loot drops</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Defeated enemies can trigger loot drops during battle. On wipeout: all loot drops are LOST. Only victory commits loot to inventory.</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Defeat Rewards</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Gold on wipeout</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>On wipeout: player keeps 50% of gold earned from enemy kills during the battle. Other 50% is lost.</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Defeat Rewards</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Quest rewards on defeat</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Quest rewards CANNOT be obtained on defeat. Quest progress is NOT advanced. The quest remains incomplete.</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Defeat Rewards</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Guild XP penalty</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Wipeout or escape penalizes Guild XP. Exact penalty formula pending design. Direction: reduced or zero Guild XP from failed battles, possible negative Guild XP modifier for consecutive failures.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Locked direction — exact formula pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Defeat Rewards</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Escape</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Escaping a battle follows the same reward rules as wipeout: keep kill XP, keep 50% gold, lose all loot, no quest progress, Guild XP penalty.</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Locked direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Defeat Rewards</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Persistent HP/MP on defeat</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Persistent HP/MP loss still applies on defeat. Units end battle at their current HP/MP. KO'd units follow KO recovery rules. No post-battle 35% recovery on defeat.</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Victory Rewards</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Victory: 100% kill XP + 100% gold + all loot committed + quest progress + quest rewards + full Guild XP + post-battle 35% recovery.</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Design Principle</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Basics always affordable. Everything at once is impossible. Free player covers necessities (~69% of income) with surplus for partial luxury progression.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Kill Gold Formula</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Kill Gold = Base Gold × (1 + Enemy Level / 100). Scales at half the rate of XP (Level/100 vs Level/50) — intentional scarcity.</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Kill Gold — Grunt</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Base Gold = 8</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Kill Gold — Veteran</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Base Gold = 14</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Kill Gold — Elite</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Base Gold = 25</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Kill Gold — Boss</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Base Gold = 50</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Kill Gold — Overleveled Penalty</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Same bands as XP: gap ≤5 ×1.0, 6-10 ×0.75, 11-15 ×0.50, 16-20 ×0.25, 21+ ×0.10. Underleveled content gives NO bonus gold (prevents gold farming in hard content).</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Battle Completion Gold</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Base × (1 + Map Level / 50). Normal = 30, Elite = 50, Boss = 100, Survive/Protect = 40, Exploration = 25.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Quest Reward Gold</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Base × (1 + Recommended Level / 40). Shown upfront before acceptance. Normal = 50, Elite = 80, Boss = 150, Exploration = 120, Dispatch = 40.</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Gold Sources</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Fortune Gold Multiplier</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>1 + 0.50 × Normalized Expedition Fortune. Max theoretical ×1.50. Applies to expedition-generated gold only.</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Locked — see loot_progression table</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Item Value</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Base Value by Slot</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>1H = 100, 2H = 150, Off-Hand = 60, Body = 80, Head = 60, Gloves = 50, Feet = 50, Accessory = 70.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Item Value</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Rarity Multiplier</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Broken = 0.1, Common = 1.0, Uncommon = 1.5, Rare = 2.5, Epic = 4.0, Legendary = 7.0, Mythic = 12.0, Transcendent = 20.0, Unique = 15.0.</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Item Value</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Level Multiplier</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>1 + (Item Level - 1) × 0.02. L1 = ×1.00, L50 = ×1.98, L99 = ×2.96.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Item Value</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Sell Value Formula</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>floor(Base Value × Rarity Mult × Level Mult × 0.25). Supplementary income source (~6% of total income).</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Shop Price Formula</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>round(Base Value × Rarity Mult × Level Mult × 4.0). Shop Markup = ×4.0.</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Buy/Sell Ratio</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>16:1. Shop markup ×4.0 / Sell rate ×0.25. No profitable buy-sell loops.</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Purchasing Power Stability</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>A level-appropriate Common weapon costs 2.5-2.7 battles at ANY level. Stable purchasing power across the full game.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>Shop Stock</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Shops sell Common and Uncommon items up to current Map Level. Rare+ items are NOT available in shops — loot or blacksmith only. Merchant stock rotation rules pending.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Locked direction — rotation details pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade Gold Cost Formula</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>floor(Base Value × Rarity Mult × 0.30 × (1 + Target Level / 25)). Per level. Plus materials (separate design).</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>Locked — materials system pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Upgrade Cost Feel</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Rare weapon +30 levels ≈ 4 battles. Legendary weapon +25 levels ≈ 12 battles. Primary gold sink (~43% of lifetime income).</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Downgrade</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Free. No gold, materials, or compensation. Reduces item level so lower-level units can equip it.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Fee Formula</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>200 + (Unit Level × 15) + Quality Premium. Standard = +0, Quality = +300, Elite = +800.</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Fee Feel</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>L1 Standard = 215g (1.3 battles). L50 Standard = 950g (3.1 battles). L50 Elite = 1750g (5.8 battles). Small portion of total spend (~2%).</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Inventory Maintenance</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>50 items. Items beyond threshold incur per-visit maintenance cost.</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Locked — tunable during testing</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Inventory Maintenance</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Cost Formula</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>min(Excess Items × 5, 200) gold per base visit. Excess = max(0, Item Count - 50).</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Locked — cap and per-item rate tunable</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Dispatch</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>50 gold per dispatch mission. Base 3 concurrent slots.</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>Consumables</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Pricing Direction</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>Individual consumable prices pending. Average ~50g per consumable. ~6% of lifetime income.</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Locked direction — individual prices pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Guild Facilities</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>Long-term gold sink. Luxury progression (~44% of lifetime income). Cannot fully complete L1→L99 on free income alone — creates endgame engagement.</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Locked direction — individual facility costs pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Guild Facilities</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Estimated Curve</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>500 + (Guild Level × 200) per facility level. L1→L25 total ≈ 77,500g. Exact per-facility costs pending.</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Placeholder — pending Slice 8 design</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Robux Convenience</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Design Principle</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Convenience boosts only. No exclusive power. A boosted player with the same gear at the same level has zero combat advantage over a free player.</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Robux Convenience</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Gold Boost</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>+25% battle gold. Time-limited (24h / 7d / 30d). Moves lifetime expense ratio from 113% to 90% — makes guild facilities reachable without trivializing choices.</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Robux Convenience</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>XP Boost</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>+25% battle XP. Time-limited (24h / 7d / 30d).</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Robux Convenience</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Inventory Expansion</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>+25 item threshold per purchase. Permanent. Reduces maintenance costs.</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Robux Convenience</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Dispatch Slot</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>+1 concurrent dispatch slot (base 3, max 6). Permanent.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Robux Convenience</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Cosmetics</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Unit skins, HQ decoration, portraits, name changes. Permanent. No gameplay impact.</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Robux Convenience</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Robux CANNOT Buy</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Equipment, stats, levels, skill/augment/doctrine cards, materials, gold directly, exclusive content, rarity upgrades, recruitment shortcuts, combat advantage of any kind.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Robux Convenience</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Robux Price Points</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Pending Roblox marketplace research.</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Economy Phases</t>
+        </is>
+      </c>
+      <c r="B39" s="8" t="inlineStr">
+        <is>
+          <t>L1-20 (Early)</t>
+        </is>
+      </c>
+      <c r="C39" s="8" t="inlineStr">
+        <is>
+          <t>Gold flows freely. Buy basic gear, recruit early. Blacksmith affordable. Feels generous — hooks the player.</t>
+        </is>
+      </c>
+      <c r="D39" s="8" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Economy Phases</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>L20-50 (Mid)</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Meaningful choices emerge. Upgrade or buy? Which unit? Guild facilities start competing for gold.</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Economy Phases</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>L50-80 (Late)</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Tight. Legendary upgrades expensive. Must loot-hunt for Rare/Epic drops to reduce shop dependence.</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Economy Phases</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>L80-99 (Endgame)</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Scarcity. Guild facilities vs final gear upgrades. Gold Boost feels genuinely helpful, not mandatory.</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="inlineStr">
+        <is>
+          <t>Lifetime Income (L1→L99, ~547 battles)</t>
+        </is>
+      </c>
+      <c r="C43" s="8" t="inlineStr">
+        <is>
+          <t>Battle gold ~165,000g + sell income ~10,800g = ~175,800g total.</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>Necessities Cost</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>~121,000g (69% of income). Recruitment + shop + blacksmith + consumables + ongoing.</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>Luxuries Cost</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>~78,000g (44% of income). Guild facilities. Cannot complete everything — intentional.</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>Free Player</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Covers all basics. Guild facilities up to ~L18 before deficit.</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>Boosted Player (+25%)</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Covers basics + guild to ~L22. Expense ratio 90%.</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Material Tiers</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Design Principle</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>5 generic tiers, one material type per tier. No element-specific or slot-specific materials. The tier alone gates difficulty. Prevents frustrating RNG ('I need Fire Shards but only get Ice Shards').</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Material Tiers</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>T1 — Rough Fragment</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Gray. Drops from L1-25 content. Common drops, early chests.</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Material Tiers</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>T2 — Refined Shard</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Green. Drops from L20-50 content. Mid-game drops, quests.</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Material Tiers</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>T3 — Polished Core</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Blue. Drops from L40-70 content. Elite encounters, late-mid drops.</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Material Tiers</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>T4 — Pristine Crystal</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Purple. Drops from L60-90 content. Boss encounters, endgame drops.</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Material Tiers</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>T5 — Ethereal Essence</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Gold. Drops from L80-99 content. Daily events (only reliable source), rare L80+ boss drops, L90+ elite encounters.</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Normal Enemy Kill</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="inlineStr">
+        <is>
+          <t>20% chance per kill. 1 material. Tier based on enemy level range. Primary source (~1.6 per battle from 8 enemies).</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Elite Encounter</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>75% chance (1 guaranteed if rewarded). 2-3 materials. Tier = enemy level range.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Boss Encounter</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>100% guaranteed. 3-5 materials. Tier = boss level range.</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Treasure Chest</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>100% on Interact. 1-2 materials + other loot.</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Locked — already in objects_encounters</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Quest Reward</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Shown upfront before acceptance. Varies by quest type and recommended level.</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Dispatch Reward</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Shown upfront. 1-3 materials, lower tier than current content.</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Daily Event</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>100% event reward. T5 Ethereal Essence exclusively. Only reliable T5 source.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Destroyed Objects</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>30% chance with Salvager's Cap passive. 1 material.</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Locked — already in nonweapon_equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Drop Sources</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Average Per Battle</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>~2.6 materials per battle total (kills 1.6 + quest 0.5 + chest 0.3 + elite/boss 0.2).</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Drop Tier Rules</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Tier Assignment</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Material tier dropped matches content level range: L1-20 → T1, L21-40 → T2, L41-60 → T3, L61-80 → T4, L81-99 → T5.</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Drop Tier Rules</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Overlap Handling</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Overlapping level ranges (e.g. L20 content) weighted toward lower tier.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Drop Tier Rules</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>T5 Restriction</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>T5 Ethereal Essence ONLY from: daily events, L80+ boss encounters, and L90+ elite encounters. No other source.</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Drop Tier Rules</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Fortune Exclusion</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Fortune does NOT affect material drop rate, quantity, or tier. Materials are deterministic progression, not luck-gated.</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Locked — per loot_progression rules</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Blacksmith Recipes</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Upgrade Recipe</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Each upgrade level requires Gold (from economy_framework) + Materials. Material tier = based on target item level. Material quantity = based on item rarity.</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith Recipes</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Tier by Target Level</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Target L1-20: T1. Target L21-40: T2. Target L41-60: T3. Target L61-80: T4. Target L81-99: T5.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith Recipes</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Quantity by Rarity</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Common = 1/level, Uncommon = 1/level, Rare = 2/level, Epic = 3/level, Legendary = 4/level, Mythic = 5/level, Transcendent = 6/level.</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith Recipes</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Example — Rare 1H L50→L55</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Gold: 1,170g + Materials: 10× T3 Polished Core (5 levels × 2/level).</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith Recipes</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Example — Legendary 1H L65→L90</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Gold: ~16,500g + Materials: 60× T4 Pristine Crystal (15 levels × 4/level for L66-80) + 40× T5 Ethereal Essence (10 levels × 4/level for L81-90).</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Material Conversion</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Conversion Formula</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>3× lower tier → 1× next tier. One-way, lossy. Available at Blacksmith facility.</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Material Conversion</t>
+        </is>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Purpose</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Prevents hoarding of low-tier materials. Excess T1/T2 becomes useful for endgame T3/T4 upgrades. Safety net for tight T3/T4 budgets.</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Material Conversion</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Chain Example</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>281 surplus T1 → ~93 T2 → ~31 T3 → ~10 T4. Covers shortfalls from aggressive upgrading.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Material Sell</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Sell to Merchant</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>T1 = 5g, T2 = 15g, T3 = 40g, T4 = 100g, T5 = 250g. Emergency gold conversion. Deliberately poor exchange rate — upgrading is always better value.</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Storage Model</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>Materials are NOT items. They do not count toward inventory threshold. Stored as 5 integer counters: T1_count through T5_count.</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Save Location</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>DataStore Key 2 (Inventory + Currencies) alongside gold. Minimal save space: 5 integers.</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>No Hard Cap</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>No maximum material count. Conversion sink and guild facility sink prevent unbounded hoarding.</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Guild Facility Sink</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Direction</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Some guild facility levels require materials alongside gold. Specific tiers and quantities TBD per facility during Slice 8 design.</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Locked direction — details pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>UI Presentation</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Inventory Display</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="inlineStr">
+        <is>
+          <t>Shown as 5 colored crystal/gem icons with count. Color-coded: Gray (T1), Green (T2), Blue (T3), Purple (T4), Gold (T5).</t>
+        </is>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Locked — Slice 7 presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>UI Presentation</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith Preview</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Shown in upgrade cost preview alongside gold: e.g. 'Cost: 1,170g + 10× Polished Core'.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Locked — Slice 7 presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>UI Presentation</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Reward Preview</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Shown in quest/dispatch reward preview alongside gold and items.</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>Locked — Slice 7 presentation</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Lifetime Income (L1→L99)</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
+        <is>
+          <t>T1: ~286, T2: ~286, T3: ~286, T4: ~286, T5: ~312 (includes daily events). Total ~1,456 materials.</t>
+        </is>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Realistic Spend (10 upgrades)</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>T1: 5, T2: 100, T3: 255, T4: 255, T5: 55. Total 670 materials.</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>T3/T4 Budget</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>89% used on realistic 10-upgrade scenario. Tight but positive with conversion safety net. Aggressive upgraders (10+ items) need targeted farming or conversion.</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>Design Feel</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Gold remains primary constraint. Materials are secondary — tight at T3/T4, comfortable at T1/T2, daily-gated at T5. Materials add a second resource axis without replacing gold as primary sink.</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
         </is>
       </c>
     </row>

--- a/docs/CTRBLXAI_Game_Rules.xlsx
+++ b/docs/CTRBLXAI_Game_Rules.xlsx
@@ -40,9 +40,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="21 Unit Progression" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="22 Economy Framework" sheetId="32" state="visible" r:id="rId32"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="23 Materials System" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24 Consumable Prices" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25 Guild Facilities" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01 Project Identity'!$A$1:$D$79</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'02 Core Stats Formulas'!$A$1:$D$49</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'03 Movement Targeting'!$A$1:$D$73</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'04 Elements Statuses'!$A$1:$D$52</definedName>
@@ -92,7 +93,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -123,6 +124,30 @@
         <bgColor rgb="002F5496"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E4D5F0"/>
+        <bgColor rgb="00E4D5F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -142,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +188,18 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -530,8 +567,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D108"/>
+  <dimension ref="A1:D123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -558,364 +601,323 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Core Identity</t>
+          <t>Core Identity — Medieval-fantasy tactical RPG with RT timeline, AP turns, square-grid movement, elevation, deterministic resolution, procedural generation, and persistent unit identity.</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Medieval-fantasy tactical RPG with RT timeline, AP turns, square-grid movement, elevation, deterministic resolution, procedural generation, and persistent unit identity.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
           <t>Manual Overview</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Deployment Target</t>
+          <t>Deployment Target — Roblox Studio</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Roblox Studio</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>Manual Overview</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Current Prototype</t>
+          <t>Current Prototype — 8x8 board is for testing only. Intended maps: 20x20 to 40x40 depending on battle type.</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>8x8 board is for testing only. Intended maps: 20x20 to 40x40 depending on battle type.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
           <t>Manual Overview</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Max Deployment</t>
+          <t>Max Deployment — Maximum player-controlled deployment is 7 units. Standard PvE encounters generally contain at least two more enemies than player units.</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Maximum player-controlled deployment is 7 units. Standard PvE encounters generally contain at least two more enemies than player units.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
           <t>Manual Overview</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Core identity</t>
+          <t>Core identity — Medieval-fantasy tactical RPG with RT timeline, AP turns, square-grid movement, elevation, deterministic combat, and strong status interactions.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Medieval-fantasy tactical RPG with RT timeline, AP turns, square-grid movement, elevation, deterministic combat, and strong status interactions.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>Manual Overview</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Current prototype</t>
+          <t>Current prototype — 8x8 board is for testing only. Intended maps may range from 20x20 to 40x40 depending on battle type.</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8x8 board is for testing only. Intended maps may range from 20x20 to 40x40 depending on battle type.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
           <t>Manual Overview</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Deployment target</t>
+          <t>Deployment target — Maximum player-controlled deployment is 7 units. Standard PvE encounters generally contain at least twice the deployed player-unit count; at maximum deployment, a normal PvE encounter should generally contain at least approximately 14 enemies. This is encounter guidance, not an absolute enemy-count formula.</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maximum player-controlled deployment is 7 units. Standard PvE encounters generally contain at least twice the deployed player-unit count; at maximum deployment, a normal PvE encounter should generally contain at least approximately 14 enemies. This is encounter guidance, not an absolute enemy-count formula.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
           <t>Manual Overview</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Obsolete terms</t>
+          <t>Obsolete terms — Speed, SPD, FFT-style unit CT meter, Accuracy, Miss Chance, Critical Hit, RES, separate Magic Defense.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Speed, SPD, FFT-style unit CT meter, Accuracy, Miss Chance, Critical Hit, RES, separate Magic Defense.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
           <t>Manual Overview</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Authority</t>
+          <t>Authority — Skills, Augments, Doctrines, and Trigger Recursion are the authoritative detailed catalogs. Subject-rule sheets in this workbook are canonical for their domains. Archived workbooks do not override this implementation manual.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Skills, Augments, Doctrines, and Trigger Recursion are the authoritative detailed catalogs. Subject-rule sheets in this workbook are canonical for their domains. Archived workbooks do not override this implementation manual.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
           <t>Consolidation rule</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Authority</t>
+          <t>Authority — Most recently approved conversation decision supersedes earlier manual text when conflict exists.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Most recently approved conversation decision supersedes earlier manual text when conflict exists.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Guard</t>
+          <t>Guard — Guard (Dispellable Buff Status)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Guard reduces eligible incoming final damage by 35%; maximum total Guard reduction is 80%.</t>
+          <t>Guard reduces eligible incoming final damage by 35%; maximum total Guard reduction is 80%. Guard is a dispellable buff status managed through StatusService. Duration: 1 turn (until next ready turn). Dispellable by Purge/Dispel. Removed by hard CC (Stun, Freeze, Sleep). Visible in status bar.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Guard exclusions</t>
+          <t>Guard exclusions — Collision damage, fall damage, hazards, debuffs, statuses, forced movement, and other non-direct effects are not covered unless explicit.</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Collision damage, fall damage, hazards, debuffs, statuses, forced movement, and other non-direct effects are not covered unless explicit.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Guard Stability</t>
+          <t>Guard Stability — Guard grants a Stability bonus while active; exact value remains pending.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Guard grants a Stability bonus while active; exact value remains pending.</t>
+          <t>Pending value</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pending value</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Armor Off-Hand WT</t>
+          <t>Armor Off-Hand WT — Passive shield Defense is free outside Guard. Armor Off-Hand WT does not increase Base RT. Guard RT adds 50% of Effective Armor Off-Hand WT.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Passive shield Defense is free outside Guard. Armor Off-Hand WT does not increase Base RT. Guard RT adds 50% of Effective Armor Off-Hand WT.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Off-Hand slot ownership</t>
+          <t>Off-Hand slot ownership — A shield or Armor Off-Hand occupies the off-hand slot, uses the reserved 350 BP flexibility of a 1H setup, and is incompatible with a 2H weapon.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>A shield or Armor Off-Hand occupies the off-hand slot, uses the reserved 350 BP flexibility of a 1H setup, and is incompatible with a 2H weapon.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Weapon WT</t>
+          <t>Weapon WT — Weapon WT applies to Basic Attacks and may be inherited by Skill Cards only when the Skill explicitly declares Weapon WT Inheritance. Each Skill Card explicitly declares whether and how much Effective Weapon WT it inherits from its equipped main-hand weapon. Effective Weapon WT uses the normal weapon-WT formula and STR reduction. Focus uses the same Weapon WT pricing, STR reduction, and inheritance rules as other weapon families. A Focus may provide additional Skill-support passives, but Focus is not the only weapon family whose WT may be inherited by a Skill.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Weapon WT applies to Basic Attacks and may be inherited by Skill Cards only when the Skill explicitly declares Weapon WT Inheritance. Each Skill Card explicitly declares whether and how much Effective Weapon WT it inherits from its equipped main-hand weapon. Effective Weapon WT uses the normal weapon-WT formula and STR reduction. Focus uses the same Weapon WT pricing, STR reduction, and inheritance rules as other weapon families. A Focus may provide additional Skill-support passives, but Focus is not the only weapon family whose WT may be inherited by a Skill.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Universal weapon passive delivery</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Built-in weapon passives apply to a Skill Card only when compatibility is established through the passive’s declared Compatible Skill Tags and Compatible Target Rules.
+          <t>Universal weapon passive delivery — Built-in weapon passives apply to a Skill Card only when compatibility is established through the passive’s declared Compatible Skill Tags and Compatible Target Rules.
 After compatibility is established, the passive resolves according to its declared delivery rule.
 Delivery may be:
 - Once per Skill action
@@ -926,224 +928,224 @@
 Weapon RT Delay applies to a Skill Card only when that Skill explicitly declares Weapon RT Delay Inheritance. Weapon RT Delay is not automatically delivered by every Skill Card.</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Negative Weapon Defense</t>
+          <t>Negative Weapon Defense — Cannot fall below negative balanced Armor Defense at the same Item Level.</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cannot fall below negative balanced Armor Defense at the same Item Level.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Negative RT Delay</t>
+          <t>Negative RT Delay — Minimum base RT Delay = -150; target RT cannot go below 0; maximum BP refund = -100.</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Minimum base RT Delay = -150; target RT cannot go below 0; maximum BP refund = -100.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Hook</t>
+          <t>Hook — Parked. Complete effect, compatible Skill Tags, compatible Target Rules, delivery rule, timing, and final BP price are not approved. Do not use the former 80 BP value as a current rule.</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Parked. Complete effect, compatible Skill Tags, compatible Target Rules, delivery rule, timing, and final BP price are not approved. Do not use the former 80 BP value as a current rule.</t>
+          <t>Parked</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Parked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Weapon catalog</t>
+          <t>Weapon catalog — The current weapon catalog remains provisional and incomplete. The conventional weapon archetypes retain their approved working endpoints. The Focus Weapon Family is an approved conceptual family whose numerical archetypes and endpoints remain pending. Do not treat the current archetype count as final or authoritative.</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The current weapon catalog remains provisional and incomplete. The conventional weapon archetypes retain their approved working endpoints. The Focus Weapon Family is an approved conceptual family whose numerical archetypes and endpoints remain pending. Do not treat the current archetype count as final or authoritative.</t>
+          <t>Current / Pending Focus archetypes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Current / Pending Focus archetypes</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rarity bonus BP</t>
+          <t>Rarity bonus BP — Rarity determines positive BP allowance for bonus attributes only. Base weapon stats are ignored. Negative bonus BP is not permitted.</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Rarity determines positive BP allowance for bonus attributes only. Base weapon stats are ignored. Negative bonus BP is not permitted.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unique</t>
+          <t>Unique — Authored or curated; may have bonus attributes and ignore ordinary Weapon Builder BP limits; not automatically stronger than Transcendent.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Authored or curated; may have bonus attributes and ignore ordinary Weapon Builder BP limits; not automatically stronger than Transcendent.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Deployment limit</t>
+          <t>Deployment limit — Maximum player-controlled deployment is 7 units. Normal PvE encounters generally contain at least twice deployed player-unit count; at max deployment, approximately 14 enemies is guidance, not a formula.</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Maximum player-controlled deployment is 7 units. Normal PvE encounters generally contain at least twice deployed player-unit count; at max deployment, approximately 14 enemies is guidance, not a formula.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DEX Interaction Efficiency</t>
+          <t>DEX Interaction Efficiency — Map objects explicitly opt in and declare affected property. Universal DEX Interaction Efficiency is removed; object-by-object classification remains pending.</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Map objects explicitly opt in and declare affected property. Universal DEX Interaction Efficiency is removed; object-by-object classification remains pending.</t>
+          <t>Locked / Pending catalog</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Locked / Pending catalog</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Focus weapons</t>
+          <t>Focus weapons — Focus is a weapon family for Skill Card interactions. Focus provides no Spell Power and does not replace authored Skill Card Base Power. Exact Focus passive BP prices and archetypes remain pending.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Focus is a weapon family for Skill Card interactions. Focus provides no Spell Power and does not replace authored Skill Card Base Power. Exact Focus passive BP prices and archetypes remain pending.</t>
+          <t>Locked / Pending prices</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Locked / Pending prices</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Focus LoS bypass</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Eligible Focus LoS bypass removes LoS plus intervening unit, terrain, object, and direct projectile-path blocking. It does not remove range, target validity, occupancy, area elevation, or Skill-specific restrictions.
+          <t>Focus LoS bypass — Eligible Focus LoS bypass removes LoS plus intervening unit, terrain, object, and direct projectile-path blocking. It does not remove range, target validity, occupancy, area elevation, or Skill-specific restrictions.
 Unified Skill compatibility metadata remains pending. Before this passive can be assigned a final BP price or used in normal Focus endpoint validation, it must explicitly declare:
 - Compatible Skill effect tags
 - Compatible Target Rules
@@ -1155,293 +1157,293 @@
 The approved bypass effect remains locked. Its compatibility metadata and BP price are not yet approved.</t>
         </is>
       </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Locked effect / compatibility and price pending</t>
+        </is>
+      </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Locked effect / compatibility and price pending</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Weapon passive delivery safety</t>
+          <t>Weapon passive delivery safety — Bleed, Raptured, and Wounded evolution can advance by no more than one stage per successful hit; a status created by an evolution cannot recursively trigger another evolution during the same hit.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bleed, Raptured, and Wounded evolution can advance by no more than one stage per successful hit; a status created by an evolution cannot recursively trigger another evolution during the same hit.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Procedural pattern conversions</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Normal procedural Line 2, Impact Splash, Cleave, Cone, Adjacent, and Chain conversions cost 250 BP, are Single-base only unless restricted, replace Single, and cannot coexist with another Pattern conversion.
+          <t>Procedural pattern conversions — Normal procedural Line 2, Impact Splash, Cleave, Cone, Adjacent, and Chain conversions cost 250 BP, are Single-base only unless restricted, replace Single, and cannot coexist with another Pattern conversion.
 The converted Pattern applies to Basic Attacks and to Skill Cards only when the Skill explicitly inherits Weapon Pattern.
 Compatible weapon passives resolve through the converted Pattern according to each passive’s declared Skill-tag compatibility, Target Rules, and delivery frequency.
 Weapon RT Delay resolves through the converted Pattern for Basic Attacks and for Skill Cards only when the Skill explicitly declares Weapon RT Delay Inheritance.</t>
         </is>
       </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Impact Splash</t>
+          <t>Impact Splash — Projectile only. Primary Target receives 100% damage; four cardinally adjacent splash tiles receive 50% damage. Friendly fire applies under normal pattern rules. Splash is centered on the impact tile; Maximum Range does not enlarge splash.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Projectile only. Primary Target receives 100% damage; four cardinally adjacent splash tiles receive 50% damage. Friendly fire applies under normal pattern rules. Splash is centered on the impact tile; Maximum Range does not enlarge splash.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Extended Reach</t>
+          <t>Extended Reach — Extended Reach I = 150 BP for Maximum Attack Range +1; Extended Reach II = 300 BP for +2. Only one tier may roll. No global Maximum Range cap is established.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Extended Reach I = 150 BP for Maximum Attack Range +1; Extended Reach II = 300 BP for +2. Only one tier may roll. No global Maximum Range cap is established.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Close-Quarters Mechanism</t>
+          <t>Close-Quarters Mechanism — Projectile ranged only. Tier I = 75 BP for Minimum Range -1; Tier II = 150 BP for -2. Final Minimum Range cannot fall below 1 and only one tier may roll.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Projectile ranged only. Tier I = 75 BP for Minimum Range -1; Tier II = 150 BP for -2. Final Minimum Range cannot fall below 1 and only one tier may roll.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Rarity ladder</t>
+          <t>Rarity ladder — Broken, Common, Uncommon, Rare, Epic, Legendary, Mythic, Transcendent, Unique. Normal procedural equipment budgets and tolerance bands are locked in Item Rarity Generation.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Broken, Common, Uncommon, Rare, Epic, Legendary, Mythic, Transcendent, Unique. Normal procedural equipment budgets and tolerance bands are locked in Item Rarity Generation.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Fortune formulas</t>
+          <t>Fortune formulas — Drop, quality, rarity weighting, and Gold formulas are locked in Activities and Loot / LUK Fortune Discovery. Fortune is multiplicative, cannot unlock ineligible rarity, and cannot add slots or change categories.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Drop, quality, rarity weighting, and Gold formulas are locked in Activities and Loot / LUK Fortune Discovery. Fortune is multiplicative, cannot unlock ineligible rarity, and cannot add slots or change categories.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Passive Ownership and Break framework</t>
+          <t>Passive Ownership and Break framework — Locked in v0.8. Break affects only Doctrine Passive, Race Passive, Inherent Unit Perk, and Inherent Unit Drawback. Race Tags and equipment passives remain active; equipment statistics, affixes, structural properties, existing effects, Skill Cards, Augments, and summons are not disabled.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Locked in v0.8. Break affects only Doctrine Passive, Race Passive, Inherent Unit Perk, and Inherent Unit Drawback. Race Tags and equipment passives remain active; equipment statistics, affixes, structural properties, existing effects, Skill Cards, Augments, and summons are not disabled.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Skill Card property inheritance</t>
+          <t>Skill Card property inheritance — Skill Cards do not automatically inherit every equipped-weapon property. Each Card explicitly declares inherited statistics/properties, how each is multiplied/converted/scaled, the affected mechanic, and binary compatibility requirements. Possible declared sources include Weapon Defense.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Skill Cards do not automatically inherit every equipped-weapon property. Each Card explicitly declares inherited statistics/properties, how each is multiplied/converted/scaled, the affected mechanic, and binary compatibility requirements. Possible declared sources include Weapon Defense.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Weapon Defense distinction</t>
+          <t>Weapon Defense distinction — Weapon Defense is not a normal procedural weapon bonus roll, but existing base Weapon Defense remains a weapon property. A Skill Card may inherit or scale from Weapon Defense only when the Card explicitly declares how it does so.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Weapon Defense is not a normal procedural weapon bonus roll, but existing base Weapon Defense remains a weapon property. A Skill Card may inherit or scale from Weapon Defense only when the Card explicitly declares how it does so.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Elite encounter identity</t>
+          <t>Elite encounter identity — Elite encounters are rare random encounter events. Fortune does not affect elite encounter appearance; it affects only the eligible reward opportunity and resulting quality after completion.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Elite encounters are rare random encounter events. Fortune does not affect elite encounter appearance; it affects only the eligible reward opportunity and resulting quality after completion.</t>
+          <t>Locked / Appearance rate pending</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Locked / Appearance rate pending</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Future patch versioning</t>
+          <t>Future patch versioning — Every future manual patch must update the visible workbook title, Index manual-version entry, Version Tracking, and relevant Current Decisions / Parked Topics entries.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Every future manual patch must update the visible workbook title, Index manual-version entry, Version Tracking, and relevant Current Decisions / Parked Topics entries.</t>
+          <t>Locked process</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Locked process</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Unified Skill Card architecture</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Skill Cards are level-less authored active abilities. Each Skill explicitly declares effect tags, Target Rules, costs, formulas, weapon-property inheritance, Bonus Skill Range inheritance, eligible weapon passives, projectile behavior, pattern behavior, Skill Potency eligibility, and special rules.
+          <t>Unified Skill Card architecture — Skill Cards are level-less authored active abilities. Each Skill explicitly declares effect tags, Target Rules, costs, formulas, weapon-property inheritance, Bonus Skill Range inheritance, eligible weapon passives, projectile behavior, pattern behavior, Skill Potency eligibility, and special rules.
 Skill Potency Multiplier = 1 + INT / (200 + INT).
 Skill Potency Bonus = Skill Potency Multiplier - 1.
 Every Skill Card explicitly declares whether Skill Potency applies and identifies the damage, healing, shield, or other approved formula component it modifies.
@@ -1449,26 +1451,26 @@
 No separate Spell Power stat exists.</t>
         </is>
       </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Max MP and Bonus Skill Range</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Max MP = 20 + INT x 2.
+          <t>Max MP and Bonus Skill Range — Max MP = 20 + INT x 2.
 Bonus Skill Range = floor(INT / 75) + Flat Skill Range Bonuses.
 Every Skill Card explicitly declares its Skill Range Inheritance percentage.
 Default Skill Range Inheritance is 100%.
@@ -1479,886 +1481,893 @@
 Use the Manual’s global rounding rule where .5 rounds up.</t>
         </is>
       </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Effective Skill Level</t>
+          <t>Effective Skill Level — Effective Skill Level = Main-hand Item Level. Every combat-capable unit requires a main-hand weapon and Doctrine; normal generated units require valid compatible Skill loadout.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Effective Skill Level = Main-hand Item Level. Every combat-capable unit requires a main-hand weapon and Doctrine; normal generated units require valid compatible Skill loadout.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Skill timing and costs</t>
+          <t>Skill timing and costs — Every Skill declares RT Cost, MP Cost, Channel Time, and Activation Time. Any field may be zero. There are no Skill cooldowns. MP Cost scales through Effective Skill Level, not actual Max MP.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Every Skill declares RT Cost, MP Cost, Channel Time, and Activation Time. Any field may be zero. There are no Skill cooldowns. MP Cost scales through Effective Skill Level, not actual Max MP.</t>
+          <t>Every Skill declares RT Cost, MP Cost, Channel Time, and Activation Time. Any field may be zero. There are no Skill cooldowns. MP Cost uses authored per-skill formula: round(Base + Growth × (Effective Skill Level - 1)). Effective Skill Level = Main-hand Item Level = Weapon Level. Each skill has its own base and growth rate.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Skill tags</t>
+          <t>Skill tags — Minimal current Skill tags are Direct Damage, Healing, Shield, Buff, Debuff, Utility, Summon, Physical, Fire, Water, Ice, Electric, Earth, Dark, Holy, and Poison. Physical is default non-elemental damage attribute.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minimal current Skill tags are Direct Damage, Healing, Shield, Buff, Debuff, Utility, Summon, Physical, Fire, Water, Ice, Electric, Earth, Dark, Holy, and Poison. Physical is default non-elemental damage attribute.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Weapon property inheritance</t>
+          <t>Weapon property inheritance — Every Skill explicitly declares which main-hand weapon properties it uses and how each is multiplied, converted, or applied. No automatic inheritance. Range, Pattern, and Projectile Type inheritance are always explicit.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Every Skill explicitly declares which main-hand weapon properties it uses and how each is multiplied, converted, or applied. No automatic inheritance. Range, Pattern, and Projectile Type inheritance are always explicit.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Weapon passive compatibility</t>
+          <t>Weapon passive compatibility — Weapon-passive compatibility is determined only by Skill effect tags and Target Rules. Each passive declares compatible tags/rules, effect, delivery frequency, timing, and restrictions.</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Weapon-passive compatibility is determined only by Skill effect tags and Target Rules. Each passive declares compatible tags/rules, effect, delivery frequency, timing, and restrictions.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Break framework</t>
+          <t>Break framework — Break affects only Doctrine Passive, Race Passive, Inherent Unit Perk, and Inherent Unit Drawback. Equipment passives, equipment affixes/statistics, structural properties, Basic Attack, Skill Cards, Augments, Race Tags, existing effects, and summons remain active.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Break affects only Doctrine Passive, Race Passive, Inherent Unit Perk, and Inherent Unit Drawback. Equipment passives, equipment affixes/statistics, structural properties, Basic Attack, Skill Cards, Augments, Race Tags, existing effects, and summons remain active.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Doctrine framework</t>
+          <t>Doctrine framework — Exactly 15 baseline Doctrines. Each has one fixed six-primary-stat package totaling 0% with each adjustment within ±15%, one Breakable Doctrine Passive, and exactly 3 fixed Doctrine Skill choices; select 1 active Doctrine Skill. Rarity does not alter choice count or mechanics. Doctrine Skills remain usable during Break and have exactly 2 Augment Slots.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Exactly 15 baseline Doctrines. Each has one fixed six-primary-stat package totaling 0% with each adjustment within ±15%, one Breakable Doctrine Passive, and exactly 3 fixed Doctrine Skill choices; select 1 active Doctrine Skill. Rarity does not alter choice count or mechanics. Doctrine Skills remain usable during Break and have exactly 2 Augment Slots.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Race framework</t>
+          <t>Race framework — Each Race has name, description/tags, starting primary stats, growth rates, and one Breakable Race Passive. Starting stats total 8; growth totals 2.00; no separate race benefit/drawback fields are used in current rules. Race Tags are not Breakable.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Each Race has name, description/tags, starting primary stats, growth rates, and one Breakable Race Passive. Starting stats total 8; growth totals 2.00; no separate race benefit/drawback fields are used in current rules. Race Tags are not Breakable.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Focus weapon family</t>
+          <t>Focus weapon family — Focus remains a normal weapon family using standard weapon BP target, curves, handedness, range, pattern, stat, passive, and synergy pricing. Focus is defined by a built-in passive designed to improve eligible Skill Cards.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Focus remains a normal weapon family using standard weapon BP target, curves, handedness, range, pattern, stat, passive, and synergy pricing. Focus is defined by a built-in passive designed to improve eligible Skill Cards.</t>
+          <t>Locked / endpoints pending</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Locked / endpoints pending</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Steal baseline Skill</t>
+          <t>Steal baseline Skill — Steal is a deterministic Utility Skill at fixed Range 1 with no weapon inheritance or weapon-passive compatibility. It uses authored MP/RT formulas, 200 CT Channel Time, 0 CT Activation Time, rear-position validation at activation, and one successful steal per target per battle. Exact Steal reward-pool content remains parked.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Steal is a deterministic Utility Skill at fixed Range 1 with no weapon inheritance or weapon-passive compatibility. It uses authored MP/RT formulas, 200 CT Channel Time, 0 CT Activation Time, rear-position validation at activation, and one successful steal per target per battle. Exact Steal reward-pool content remains parked.</t>
+          <t>Locked / reward pool parked</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Locked / reward pool parked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Highest-priority dependency</t>
+          <t>Highest-priority dependency — 1. Baseline Skill Card simulation and numerical calibration; 2. Focus passive definitions and normal BP pricing; 3. Focus archetype endpoint completion; 4. Consumable Architecture; 5. Skill Card Acquisition and Scarcity; 6. Augment Card Acquisition and Scarcity; 7. Doctrine Acquisition, Rarity, and Fortune; 8. Armor BP Framework; 9. Accessory BP Framework; 10. Shield and Armor Off-Hand BP Framework.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1. Baseline Skill Card simulation and numerical calibration; 2. Focus passive definitions and normal BP pricing; 3. Focus archetype endpoint completion; 4. Consumable Architecture; 5. Skill Card Acquisition and Scarcity; 6. Augment Card Acquisition and Scarcity; 7. Doctrine Acquisition, Rarity, and Fortune; 8. Armor BP Framework; 9. Accessory BP Framework; 10. Shield and Armor Off-Hand BP Framework.</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Representative Skill explicit AP Cost</t>
+          <t>Representative Skill explicit AP Cost — All 29 representative Skills explicitly record AP Cost. The current baseline uses 1 AP for every representative Skill under the approved global default.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>All 29 representative Skills explicitly record AP Cost. The current baseline uses 1 AP for every representative Skill under the approved global default.</t>
+          <t>Working simulation baseline</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Working simulation baseline</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Representative Skill Targeting Range completeness</t>
+          <t>Representative Skill Targeting Range completeness — Every representative Skill explicitly records its targeting-range source. All 29 have working fixed, formula-based, movement-based, or complete Weapon Range inheritance rules. No representative targeting range remains blank or marked Pending working simulation range.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Every representative Skill explicitly records its targeting-range source. All 29 have working fixed, formula-based, movement-based, or complete Weapon Range inheritance rules. No representative targeting range remains blank or marked Pending working simulation range.</t>
+          <t>Working simulation baseline</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Working simulation baseline</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Representative Skill Augment Slot completeness</t>
+          <t>Representative Skill Augment Slot completeness — Every representative Skill and every future Skill Card has exactly 2 Augment Slots. This includes Doctrine-provided Skills and Steal. Slot count does not vary by Skill type, rarity, source, tags, power, complexity, costs, timing, inheritance, projectile behavior, Pattern, AOE behavior, or acquisition source.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Every representative Skill and every future Skill Card has exactly 2 Augment Slots. This includes Doctrine-provided Skills and Steal. Slot count does not vary by Skill type, rarity, source, tags, power, complexity, costs, timing, inheritance, projectile behavior, Pattern, AOE behavior, or acquisition source.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ordinary Dual-Wield Doctrine baseline</t>
+          <t>Ordinary Dual-Wield Doctrine baseline — Ordinary dual wield requires two naturally legal 1H weapons and retains 75% of each weapon’s numerical properties. Structural properties remain intact; the shared sequential Basic Attack, Knockback, passive-delivery, Break, and main-hand-only Skill-inheritance rules apply.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ordinary dual wield requires two naturally legal 1H weapons and retains 75% of each weapon’s numerical properties. Structural properties remain intact; the shared sequential Basic Attack, Knockback, passive-delivery, Break, and main-hand-only Skill-inheritance rules apply.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Universal Skill Card Augment Slots</t>
+          <t>Universal Skill Card Augment Slots — All Skill Cards have exactly 2 Augment Slots. Doctrine-provided Skills use the same 2-slot rule. Skill rarity and source do not modify Augment Slot count.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>All Skill Cards have exactly 2 Augment Slots. Doctrine-provided Skills use the same 2-slot rule. Skill rarity and source do not modify Augment Slot count.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Representative Skill working targeting ranges</t>
+          <t>Representative Skill working targeting ranges — All 29 representative Skills now have explicit working targeting-range rules. Twenty-three formerly pending values received provisional simulation ranges. These values support comparative spatial simulation but remain working baselines, not final balance. Bonus Skill Range affects targeting distance only and never enlarges Pattern or AOE dimensions unless a Skill explicitly says otherwise.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>All 29 representative Skills now have explicit working targeting-range rules. Twenty-three formerly pending values received provisional simulation ranges. These values support comparative spatial simulation but remain working baselines, not final balance. Bonus Skill Range affects targeting distance only and never enlarges Pattern or AOE dimensions unless a Skill explicitly says otherwise.</t>
+          <t>Working simulation baseline</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Working simulation baseline</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Natural MP Regen and Persistent HP/MP</t>
+          <t>Recharge — Recharge immediately restores 10% Max MP, then restores 5% Max MP every 300 CT for four ticks over 1200 CT. Reapplication refreshes duration without repeating the immediate restoration.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>INT provides natural in-battle MP regeneration as a visible Derived Stat. MP Regen = 2 + floor(INT / 40) MP per 1000 CT. Base 2 ensures all units regenerate naturally. Every 40 INT adds +1. No cap. HP and MP persist between battles — battles start at persistent current values, NOT full. Post-battle recovery: ceil(Max × 0.35) for all surviving units. Skill MP Cost scales with Weapon Level: Effective MP Cost = ceil(Base MP Cost × Scale(Weapon Level)). Full rules: query persistent_hp_mp_rules and core_stats in CTRBLXAI.db.</t>
+          <t>Working simulation baseline</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Recharge</t>
+          <t>Mechanical Race Tag drawback — Mechanical units have Raw Weapon WT +15%. Apply this before weapon-use scaling and STR-based Weapon WT reduction.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Recharge immediately restores 10% Max MP, then restores 5% Max MP every 300 CT for four ticks over 1200 CT. Reapplication refreshes duration without repeating the immediate restoration.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Working simulation baseline</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mechanical Race Tag drawback</t>
+          <t>Power Strike working calibration — Power Strike uses Weapon Attack Power ×1.25 × Skill Potency Multiplier. Its previous ×1.50 coefficient is superseded.</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mechanical units have Raw Weapon WT +15%. Apply this before weapon-use scaling and STR-based Weapon WT reduction.</t>
+          <t>Working simulation baseline</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Power Strike working calibration</t>
+          <t>Weapon-use percentage hierarchy — Natural single 1H use retains 100%; Colossal Arsenal single converted 2H use retains 75%; ordinary dual wield retains 75% per naturally 1H weapon; Titan dual wield retains 65% per normally 2H melee weapon.</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Power Strike uses Weapon Attack Power ×1.25 × Skill Potency Multiplier. Its previous ×1.50 coefficient is superseded.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Working simulation baseline</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Weapon-use percentage hierarchy</t>
+          <t>Dual-Wield Basic Attack RT — One shared round(Modified Base RT ×0.10) component plus the Effective Reduced WT of both weapons. Dual wield does not pay two separate base-RT components.</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Natural single 1H use retains 100%; Colossal Arsenal single converted 2H use retains 75%; ordinary dual wield retains 75% per naturally 1H weapon; Titan dual wield retains 65% per normally 2H melee weapon.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Dual-Wield Basic Attack RT</t>
+          <t>Doctrine fixed-choice baseline — The baseline contains exactly 15 Doctrines. Every Doctrine has exactly 3 fixed Doctrine Skill choices and the unit selects 1 active choice. Rarity does not alter choice count; Doctrine Skills remain usable during Break and have exactly 2 Augment Slots.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>One shared round(Modified Base RT ×0.10) component plus the Effective Reduced WT of both weapons. Dual wield does not pay two separate base-RT components.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Doctrine fixed-choice baseline</t>
+          <t>Doctrine scarcity — Doctrines use one scarcity band comparable to Epic-to-Legendary equipment acquisition frequency. Scarcity does not alter the stat package, passive, fixed three choices, Skill profile, costs, timing, Augment Slots, or mechanics.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The baseline contains exactly 15 Doctrines. Every Doctrine has exactly 3 fixed Doctrine Skill choices and the unit selects 1 active choice. Rarity does not alter choice count; Doctrine Skills remain usable during Break and have exactly 2 Augment Slots.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Doctrine scarcity</t>
+          <t>Universal Augment ownership — Skills own ordinary gameplay data only. Augments own Augment compatibility requirements, effects, costs, restrictions, and conflicts. Skills do not declare individual Augment permission lists or Augment-specific exception fields.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Doctrines use one scarcity band comparable to Epic-to-Legendary equipment acquisition frequency. Scarcity does not alter the stat package, passive, fixed three choices, Skill profile, costs, timing, Augment Slots, or mechanics.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Universal Augment ownership</t>
+          <t>Augment cost model — Augments are optional specializations, not free upgrades. Costs may use MP, RT, Channel/Activation Time, positive weapon-scaling reduction, range, Pattern-to-Single, HP, or another concise authored sacrifice. Percentage costs multiply; flat costs apply afterward.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Skills own ordinary gameplay data only. Augments own Augment compatibility requirements, effects, costs, restrictions, and conflicts. Skills do not declare individual Augment permission lists or Augment-specific exception fields.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Augment cost model</t>
+          <t>Documentation-first authority — Documentation is the project priority. Completion requires every field in the authoritative schema populated, every reference resolved, every invariant validated, all active contradictions/placeholders removed, and logical combination safety documented.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Augments are optional specializations, not free upgrades. Costs may use MP, RT, Channel/Activation Time, positive weapon-scaling reduction, range, Pattern-to-Single, HP, or another concise authored sacrifice. Percentage costs multiply; flat costs apply afterward.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Documentation-first authority</t>
+          <t>Dedicated content authority — Skills, Augments, Doctrines, and Trigger Recursion are the authoritative detailed worksheets. Older sheets retain summary/history only and do not override these dedicated sheets.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Documentation is the project priority. Completion requires every field in the authoritative schema populated, every reference resolved, every invariant validated, all active contradictions/placeholders removed, and logical combination safety documented.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Dedicated content authority</t>
+          <t>Doctrine content correction — The earlier statement that the Doctrine baseline was complete was overstated. v0.9 supplies working numerical packages, complete working passives, Doctrine-only Skill profiles, and cross-sheet references. Final numerical calibration remains working, not final balance.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Skills, Augments, Doctrines, and Trigger Recursion are the authoritative detailed worksheets. Older sheets retain summary/history only and do not override these dedicated sheets.</t>
+          <t>Corrective audit record</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Doctrine content correction</t>
+          <t>Universal trigger and recursion baseline — v0.9 records examined candidate sets, state updates between Chain jumps, Augment commitment snapshots, reaction eligibility and recursion guards, Executioner and kill-trigger turn caps, primary-versus-secondary effect ownership, Explosive Death qualification, finite explosion queues, periodic propagation guards, one-pass elemental processing, HP-payment legality, Shield decay, and deterministic Break equipment legality.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The earlier statement that the Doctrine baseline was complete was overstated. v0.9 supplies working numerical packages, complete working passives, Doctrine-only Skill profiles, and cross-sheet references. Final numerical calibration remains working, not final balance.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Corrective audit record</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Universal trigger and recursion baseline</t>
+          <t>v0.9 Current Manual — CTRBLXAI Core Game Manual v0.9 is current. v0.8 and earlier versions remain historical in Version Tracking.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>v0.9 records examined candidate sets, state updates between Chain jumps, Augment commitment snapshots, reaction eligibility and recursion guards, Executioner and kill-trigger turn caps, primary-versus-secondary effect ownership, Explosive Death qualification, finite explosion queues, periodic propagation guards, one-pass elemental processing, HP-payment legality, Shield decay, and deterministic Break equipment legality.</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Locked</t>
+          <t>Current Decisions</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
+          <t>unique after exact rule-text deduplication</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>v0.9 Current Manual</t>
+          <t>Skill Scaling (NEW) — All skills scale with equipped main weapon and may additionally scale with a primary stat. The old distinction between "weapon-based skills" and "spell-based skills" is obsolete and must not be used.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CTRBLXAI Core Game Manual v0.9 is current. v0.8 and earlier versions remain historical in Version Tracking.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Current Decisions — unique after exact rule-text deduplication</t>
-        </is>
-      </c>
+          <t>Consolidation Decision 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Skill Scaling (NEW)</t>
+          <t>2H Guard RT (NEW) — If the unit is equipped with a two-handed weapon, Armor Off-Hand WT equals zero for Guard RT calculation purposes.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>All skills scale with equipped main weapon and may additionally scale with a primary stat. The old distinction between "weapon-based skills" and "spell-based skills" is obsolete and must not be used.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
           <t>Consolidation Decision 2026-08-19</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2H Guard RT (NEW)</t>
+          <t>Inventory Limit (NEW) — No hard inventory cap. Storage past a configurable threshold costs in-game currency per maintenance cycle (soft economic pressure). Exact threshold, currency, and interval are tunable during testing.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>If the unit is equipped with a two-handed weapon, Armor Off-Hand WT equals zero for Guard RT calculation purposes.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
           <t>Consolidation Decision 2026-08-19</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Inventory Limit (NEW)</t>
+          <t>Obsolete Terms — Speed, SPD, FFT-style unit CT meter, Accuracy, Miss Chance, Critical Hit, RES, separate Magic Defense. These terms must never be used.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>No hard inventory cap. Storage past a configurable threshold costs in-game currency per maintenance cycle (soft economic pressure). Exact threshold, currency, and interval are tunable during testing.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Consolidation Decision 2026-08-19</t>
-        </is>
-      </c>
+          <t>Manual Overview</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Obsolete Terms</t>
+          <t>Authority Model — Two documents: Game Rules (this file) = what the game does. Build Plan = how to implement it. They answer different questions and do not compete.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Speed, SPD, FFT-style unit CT meter, Accuracy, Miss Chance, Critical Hit, RES, separate Magic Defense. These terms must never be used.</t>
+          <t>Locked</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Manual Overview</t>
-        </is>
-      </c>
+          <t>Consolidation Decision 2026-08-19</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Authority Model</t>
+          <t>Development Progress — Slice 1 — Two Guys on a Flat Board</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Two documents: Game Rules (this file) = what the game does. Build Plan = how to implement it. They answer different questions and do not compete.</t>
+          <t>COMPLETE as of 2026-08-20. Implemented: flat grid (8x8), unit schema with HP=50+VIT*4, CT/RT timeline with full tie-breaking, 8-direction movement with diagonal cost 1.5x, basic attack using AP/HQ damage formula, skill system with registry, Chebyshev attack range (diagonal allowed), server-side AI (3-tier), client-side visual renderer (tokens, HP bars, damage numbers, animations, result banner), GameConstants shared module, BattleVisualBroadcaster pacing layer.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Consolidation Decision 2026-08-19</t>
-        </is>
-      </c>
+          <t>All Slice 1 checklist items verified complete via code audit.</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Development Progress</t>
+          <t>Development Progress — Slice 2 — Terrain and Height</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Slice 1 — Two Guys on a Flat Board</t>
+          <t>COMPLETE as of 2026-08-21. Implemented: elevation map (heights 1/2/3 with Jump restriction), terrain types (Clear/Grassland/Rocky/Mud) with movement cost multiplier, 4 blocker tiles (impassable), positional damage modifier (+/-10% per elevation level, capped 0.70–1.30), StatusService with Slow (Base RT x1.10), Crippling Shot skill (applies Slow on hit), status broadcasting and client rendering. Fall damage deferred — no forced displacement system exists yet.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>COMPLETE as of 2026-08-20. Implemented: flat grid (8x8), unit schema with HP=50+VIT*4, CT/RT timeline with full tie-breaking, 8-direction movement with diagonal cost 1.5x, basic attack using AP/HQ damage formula, skill system with registry, Chebyshev attack range (diagonal allowed), server-side AI (3-tier), client-side visual renderer, GameConstants shared module.</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>All Slice 1 checklist items verified complete via code audit.</t>
-        </is>
-      </c>
+          <t>All Slice 2 checklist items verified complete via code audit. Status effects were bonus work from Slice 3 scope.</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Development Progress — Slice 3 — Skills and Real Combat</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>COMPLETE as of 2026-08-23. Implemented: player input system (client→server via RemoteEvent, server validates via CommandService), 3v3 battles (6 units), Skill Card action prompt with target highlighting, AOE skills (Cleave pattern via Sweeping Cut), healing skill (Healing Light), MP cost enforcement with channel-then-spend logic, Poison DoT (MaxHP×0.15, 5 turns), Burn DoT (accumulated stored damage, 3 turns), full channeling system (interrupted only by disabling statuses, not damage), AI heal logic (heals low-HP allies), Content Registry (107 skills, 102 augments, 32 doctrines auto-generated from DB).</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>All Slice 3 checklist items verified complete via source code audit.</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ACTION MENU PRESENTATION</t>
-        </is>
-      </c>
+          <t>Item Generation — Item Level Assignment on Drop</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Quest rewards: Item Level = Quest Level. Loot rewards: Item Level = Enemy Level.</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Top-level menu</t>
+          <t>Natural MP Regen — MP Regen Derived Stat</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>COMMANDS | SKILLS | ITEMS | WAIT. STANCE removed.</t>
+          <t>INT provides natural in-battle MP regeneration as a visible Derived Stat. MP Regen = 2 + floor(INT / 40) MP per 1000 CT. Base 2 ensures all units regenerate. Every 40 INT adds +1. No cap. Accumulator-based, CT-elapsed (not turn-based). Battles start at persistent current MP (not full). Full rules in persistent_hp_mp_rules table.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
+          <t>Locked. Replaces former rule that INT provided no MP regen.</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Commands submenu</t>
+          <t>KO Base Recovery — KO clear HP value</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MOVE | BASIC ATTACK | GUARD | PUSH | INTERACT</t>
+          <t>When returning to base clears KO, unit receives Current HP = 1. Current MP unchanged. Unit must recover through post-battle recovery (needs ~3 battles from 1 HP to full) or healing Items/Skills in the next battle.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2366,16 +2375,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>After execution</t>
+          <t>Slice Development Model — Module Classifications</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Return to top-level if unit may continue. Do not return to submenu. If turn ends, wait for authoritative turn state.</t>
+          <t>Four types: Slice-Owned (owning slice modifies; protected after completion), Protected Completed (read-only for later slices), Shared Integration (smallest diff + approval + regression), Content Authority (Designer agent owns, Game Rules authoritative).</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2383,16 +2393,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Wait</t>
+          <t>Slice Development Model — Dependency Direction</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Top-level. If AP remains, opens confirmation before ending turn.</t>
+          <t>Authoritative rules/content → gameplay services → shared events/payloads → functional controllers → presentation views. Forbidden reverse: combat→UI, map gen→visual, save→UI state, formulas→presentation.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2400,16 +2411,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Button availability</t>
+          <t>Slice Development Model — Compatibility Process</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Never remove/hide unavailable buttons. Gray out + tooltip explaining why.</t>
+          <t>When active slice needs something unavailable from completed slice: identify missing API → check fallback → do NOT duplicate → compatibility request → approval → smallest addition → regression test → commit separately. Ownership does not transfer.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2417,16 +2429,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Availability source</t>
+          <t>Slice Development Model — Slice 7 Boundary</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Reasons come from owning functional system. Slice 7 displays but does not create gameplay rules.</t>
+          <t>Slice 7 is PRESENTATION ONLY. May define: visual composition, layout, theme, camera presentation, asset fallbacks. Must NOT define: combat formulas, legality, CT/RT, status behavior, event scheduling, server-authoritative results, database content. When data unavailable: report missing field + render fallback. Never calculate authoritative values on client.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2434,16 +2447,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Push</t>
+          <t>Action Menu — Top-Level Layout</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Visible but unavailable until Slice 2 displacement + Slice 3 command pipeline implemented.</t>
+          <t>Top-level menu: COMMANDS | SKILLS | ITEMS | WAIT. Commands submenu: MOVE | BASIC ATTACK | GUARD | PUSH | INTERACT. STANCE is removed — no universal Stance action is approved.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2451,16 +2465,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Interact</t>
+          <t>Action Menu — Commands Submenu Behavior</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Visible but unavailable until object-interaction dependencies exist.</t>
+          <t>Commands submenu remains open while choosing a universal command. After successful execution: return to top-level menu if unit may continue. Do not return to Commands submenu. If action ends turn, wait for next authoritative turn state.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2468,16 +2483,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Back/Confirm</t>
+          <t>Action Menu — Wait Confirmation</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Fixed positions: Back bottom-left, Confirm bottom-right. Stable across all menus. Confirm unavailable until selection valid.</t>
+          <t>WAIT is directly available at top level. If AP remains, WAIT opens a confirmation prompt before ending the turn.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2485,16 +2501,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Back navigation</t>
+          <t>Action Menu — Button Availability Policy</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Command targeting→Commands. Skill targeting→Skills. Item targeting→Items. Submenu→top-level.</t>
+          <t>Buttons are never removed or hidden because temporarily unavailable. Unavailable buttons: remain visible, use grayed-out style, do not initiate targeting, do not submit commands, display tooltip explaining why when selected. Examples: No valid target, Insufficient MP, Already used this turn, No interactable object in range, Not implemented yet.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2502,23 +2519,53 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Action Menu — Availability Source Rule</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Availability and rejection reasons must come from the owning functional system where available. Slice 7 formats and displays the reason but does not create gameplay availability rules.</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PUSH ACTION (Universal Command)</t>
-        </is>
-      </c>
+          <t>Action Menu — Push Button</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Push remains visible but unavailable until functional dependencies implemented. Primary functional owner: Slice 2 (displacement/terrain). Command integration owner: Slice 3 (command/targeting/validation). Slice 7 owns only: button appearance, disabled presentation, tooltip, target-highlight appearance, preview appearance, animation and result feedback.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Push AP Cost</t>
+          <t>Action Menu — Interact Button</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1 AP</t>
+          <t>Interact remains visible but unavailable until functional command and object-interaction dependencies exist. Slice 7 must not implement Interact behavior merely to activate the button.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2526,16 +2573,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Push RT Cost</t>
+          <t>Action Menu — Back and Confirm Controls</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>round(Modified Base RT x 0.10). Gloves WT already in Modified Base RT.</t>
+          <t>Back and Confirm are recurring controls with fixed positions independent of menu content. Back: bottom-left of phase-dependent panel. Confirm/Execute: bottom-right. Positions stable across Commands, Skills, Items, targeting, preview, and Wait confirmation. Confirm unavailable until selection is valid. Selecting unavailable Confirm displays missing requirement.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2543,16 +2591,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Push Range</t>
+          <t>Action Menu — Back Navigation Target</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1 (adjacent only). Gloves passives may extend.</t>
+          <t>Command targeting returns to Commands. Skill targeting returns to Skills. Item targeting returns to Items. A submenu returns to top-level menu. After successful execution, return to top-level menu if unit may continue.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2560,16 +2609,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Push Direction</t>
+          <t>Push Action — Push AP Cost</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Directly away from pusher. GL-013 overrides for adjacent.</t>
+          <t>Push costs 1 AP.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2577,16 +2627,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Push Distance</t>
+          <t>Push Action — Push RT Cost</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>max(0, Force - Target Stability) tiles.</t>
+          <t>Push RT = round(Modified Base RT × 0.10). Gloves WT is already included in Modified Base RT like all non-weapon equipment. No separate Gloves WT addition.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2594,16 +2645,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Force</t>
+          <t>Push Action — Push Base Range</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1 + floor(STR / 60)</t>
+          <t>Push Range = 1 (adjacent only). Gloves passives may add to this.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2611,16 +2663,17 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Push Action — Push Direction</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1 + floor(VIT / 60)</t>
+          <t>Push displaces target directly away from pusher (cardinal or diagonal based on relative position). GL-013 Vector Gloves overrides this for adjacent targets.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2628,23 +2681,57 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Push Action — Push Distance</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Push Distance = max(0, Force - Target Stability) tiles. Force = 1 + floor(STR/60). Stability = floor(VIT/60).</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>EQUIPMENT WT MODEL</t>
+          <t>Push Action — Push Once Per Turn</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Push may be used once per turn (same restriction as Guard).</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>pending confirmation, inferred from Guard pattern</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Non-weapon WT</t>
+          <t>Equipment WT Model — Non-Weapon WT adds to Base RT</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Body, Head, Gloves, Feet, Accessory WT adds to Base RT always.</t>
+          <t>Non-weapon equipment WT (Body, Head, Gloves, Feet, Accessory) adds to the unit's Base RT always. Only weapon WT is special — it applies only during Basic Attack or Skill actions via the Effective WT formula.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2652,50 +2739,75 @@
           <t>Locked</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Weapon WT</t>
+          <t>Development Progress — Push Action Implemented</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Only applies during Basic Attack or Skills via Effective WT formula.</t>
+          <t>Push universal command implemented across Slice 2 (DisplacementService — displacement physics, collision, fall damage) and Slice 3 (CommandService — command validation, targeting, RT, broadcasting). Base rules: 1 AP, RT = round(Modified Base RT × 0.10), Range 1, Direction directly away, Distance = max(0, Force - Stability).</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Locked</t>
-        </is>
-      </c>
+          <t>Verified 2026-08-30</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Development Progress — Slice 4 Complete — 2026-08-31</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SaveService (3-key DataStore), PersistentStateService (HP/MP/KO, recovery, MP regen), InventoryService, EquipmentService (server-validated equip/unequip), ItemGenerator (rarity/bonuses/BP), RewardService (commit-before-save), WeaponData + BonusData, roster/inventory/equip data contracts, Loadout Hub. Deferred: 18 visual items (Slice 7), Map Level placeholder (Slice 5), Doctrine Break/Augment attachment (unassigned).</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Functionally complete. Visual presentation deferred to Slice 7.</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>RNG scope</t>
+          <t>Design Philosophy — RNG scope</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>No hit/miss, dodge, or debuff infliction RNG. Combat resolution is deterministic. RNG is used for procedural generation: maps, item bonuses, loot drops, enemy spawns, recruit pools, terrain placement.</t>
+          <t>No hit/miss, dodge, or debuff infliction RNG. Combat resolution is deterministic. RNG is used for procedural generation: maps, item bonuses, loot drops, enemy spawns, recruit pools, terrain placement. RNG creates variety in content, not uncertainty in combat outcomes.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
           <t>Locked</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>clarified 2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Equipment Downgrade</t>
+          <t>Equipment Economy — Downgrade</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Downgrading equipment is FREE. No compensation. Purpose: reduce item level for lower-level unit equip. Upgrading costs gold/materials (blacksmith design pending).</t>
+          <t>Downgrading equipment is FREE. Player receives no gold, materials, or other compensation. Purpose: reduce an item's level so a lower-level unit can equip it. Upgrading costs gold and/or materials (exact costs pending blacksmith design).</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2703,9 +2815,343 @@
           <t>Locked direction</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Inventory — Equipment Slots</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Equipment inventory starts at 50 slots. Expandable via purchase (+25 slots per upgrade, Robux or in-game currency). Players should start strategizing what to keep around L50.</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Inventory — Material Storage</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Materials have SEPARATE storage from equipment. Dedicated material bag (unlimited or very large). Does not compete with equipment slots.</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Inventory — Soft Cap</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>No hard inventory cap. Maintenance cost past threshold applies to equipment only (soft economic pressure). Materials exempt.</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Races — Total Race Count</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Target: 30-50 races total. Launch with 15 designed races. Add in batches of 5-10 post-launch. Some races require unlock conditions.</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Player Avatar — Identity</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>The player avatar is the only unique unit. Flagged with is_avatar = true in unit schema. Cannot be dismissed or lost.</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Player Avatar — Race Swap</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Avatar is the only unit that can freely choose and swap race among unlocked races. Other units are permanently locked to their recruited race.</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Player Avatar — Perk/Drawback Mutation</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Avatar is the only unit whose perk and drawback can change. Changes happen ONLY through rare random dungeon exploration events. Swap only (not remove) — avatar always has exactly 1 perk and 1 drawback.</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Units — Perks/Drawbacks</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>All non-avatar units have 1 random perk and 1 random drawback assigned at recruitment. Permanent and cannot be changed.</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Races — Unlock Mechanic</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Once a race is unlocked: (1) player avatar can swap to it, (2) that race appears in recruitment pool. Unlock conditions are per-race — not yet designed.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Locked concept</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>conditions pending</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>HQ Facilities — Trophy Hall</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Trophy Hall is an HQ facility inside the base. Displays player achievements. Exact mechanics pending.</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Pending design</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>HQ Facilities — Dungeon Facility</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Dungeon is an upgradeable HQ facility. Upgrading unlocks: biome selection, dungeon difficulty/level, after-battle recovery options, and other progression features. Exact upgrade tiers pending.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Locked concept</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>tiers pending — Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Dungeons — Core Design</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>STS (Slay the Spire) style with branching node paths. Player chooses path at each fork. Node types: battle, event, shop, rest, treasure, boss. Unlike quests, battles have no guaranteed rewards.</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Dungeons — Exclusive Content</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Unique loot and rewards found ONLY in dungeons: furniture, temporary team-wide buffs/debuffs, avatar perk/drawback mutation events. Cannot be obtained from quests.</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Dungeons — vs Quests</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Dungeons and quests are separate game modes. Quests = linear battles with guaranteed loot. Dungeons = branching paths with risk/reward and exclusive content.</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Dungeons — Implementation Scope</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Slice 9 content. Requires: dungeon node-graph generation (not tile grid), node type rules, dungeon-specific reward tables, dungeon run state tracking, dungeon facility upgrade integration.</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Slice 9</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Design Session 2026-09-16</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D79"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -45554,6 +46000,6416 @@
       <c r="D40" s="9" t="inlineStr">
         <is>
           <t>Verified</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I141"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Item Name</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>Charges</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>RT</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>Shop Price (g)</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>Cost/Use (g)</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>Emergency Small Healing Potion</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Quick</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G2" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H2" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I2" s="10" t="inlineStr">
+        <is>
+          <t>Restore 30% target Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="inlineStr">
+        <is>
+          <t>Emergency Ether</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Quick</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="G3" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="H3" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I3" s="10" t="inlineStr">
+        <is>
+          <t>Restore 25% target Max MP, minimum 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Weather Gauge</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="G4" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H4" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>Reveal current weather duration and next scheduled authored change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Antidote Injector</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G5" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>Remove Poison and Venom</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>Cooling Gel Applicator</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H6" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Remove Burn and restore 10% Max HP plus stored Burn damage removed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Oil Sprayer</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Apply Oil-coated state for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>Scanner Lens</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>Reveal hidden units, traps, object properties, and deterministic Interact outcomes for 800 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Auto-Key</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>Open one standard lock up to authored tier limit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>Objective Compass</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>70</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>Reveal shortest legal path distance to known objectives for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>Mending Salve</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Restore 12% Max HP now, then 6% at 500 and 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Flash Device</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Apply Blind for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Hydraulic Sprayer</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Apply Wet and approved Water terrain interactions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Small Healing Potion</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Restore 30% target Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Ether Cell</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Restore 25% target Max MP, minimum 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Fire Flask</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F16" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Fire Power = 18 + 0.40×IL + 0.35×INT; creates Burn from damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Frost Vial</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F17" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Ice Power = 18 + 0.40×IL + 0.35×INT; may convert Wet to Frozen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Holy Water Projector</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Undead take Holy Power = 25 + 0.55×IL + 0.30×INT; non-Undead allies recover 10% Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>Strength Infuser</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H19" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>STR +15% for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>Focus Infuser</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F20" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H20" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>INT +15% for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>Stoneskin Infuser</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H21" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>VIT +15% for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>Fleetfoot Infuser</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H22" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>AGI +15% and Movement RT ×0.95 for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Precision Infuser</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H23" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>DEX +15% for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Fortune Infuser</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H24" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>LUK +20% for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>Time Crystal</t>
+        </is>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H25" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Reduce remaining RT by round(60 + 0.20×IL), minimum 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Maintenance Tool</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" s="10" t="n">
+        <v>80</v>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H26" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Restore 30% target Max HP or 200 CT duration up to original maximum.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>Shock Crystal</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F27" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H27" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Electric Power = 20 + 0.45×IL + 0.30×DEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>Acid Flask</t>
+        </is>
+      </c>
+      <c r="B28" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F28" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H28" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Poison Power = 12 + 0.30×IL + 0.25×INT; Defense −15% for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>Chrono Spike</t>
+        </is>
+      </c>
+      <c r="B29" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="10" t="n">
+        <v>85</v>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="H29" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>RT Delay = round(60 + 0.25×IL) before resistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>Magnetic Snare</t>
+        </is>
+      </c>
+      <c r="B30" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Treat Stability as 2 lower and pull 2 tiles if legal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>Weakening Projector</t>
+        </is>
+      </c>
+      <c r="B31" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F31" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G31" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H31" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>STR −20% for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>Arcane Solvent</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G32" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>INT −20% for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Interaction Amplifier</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F33" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="G33" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H33" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Next Interact before end of turn gains Maximum Range +1 and RT ×0.80.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>Weapon Jammer</t>
+        </is>
+      </c>
+      <c r="B34" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G34" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H34" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Apply Disarmed for 1500 CT; Mechanical target also receives 40 RT Delay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Net Launcher</t>
+        </is>
+      </c>
+      <c r="B35" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F35" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G35" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H35" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Center Pinned 1000 CT; adjacent units Pinned 500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Repulsion Device</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C36" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F36" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G36" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H36" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Push from center with Force = 2 + floor(IL/90) + floor(INT/150).</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Grapple Cable</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C37" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G37" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H37" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Pull with Force = 2 + floor(IL/120) + floor(STR/100).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>Armor Projector</t>
+        </is>
+      </c>
+      <c r="B38" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F38" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G38" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H38" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Equipment Defense +20% for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>Armor Corroder</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G39" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Equipment Defense −20% for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Stability Breaker</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G40" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Stability −2 for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>Purification Array</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F41" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G41" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Clean Tainted Ground and remove Poison Cloud.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Growth Catalyst</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F42" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G42" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Convert compatible Clear terrain to Grassland and strengthen existing organic cover.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>Diplomatic Seal</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F43" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G43" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Reveal recruitment requirements and prevent one failure-escalation increase.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>Recovery Winch</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F44" s="10" t="n">
+        <v>95</v>
+      </c>
+      <c r="G44" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H44" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Move target one legal tile toward user without collision or fall damage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Silence Powder Projector</t>
+        </is>
+      </c>
+      <c r="B45" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F45" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G45" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Apply Silence for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>Phase Lock</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G46" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Prevent teleport, blink, and swap for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>Cleanse Ward</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Debuff Resistance Multiplier ×0.80 for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t>Firebreak Projector</t>
+        </is>
+      </c>
+      <c r="B48" s="10" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C48" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Remove Flammable state and extinguish Burn zones along line for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Surveyor Map</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F49" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G49" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H49" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Reveal known connected Regions, roads, bridges, caves, and reachable objective routes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t>Climbing Line</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G50" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H50" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Relocate upward by up to 2 elevation to nearest legal tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Shrapnel Launcher</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F51" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="G51" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H51" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Physical Power = 22 + 0.50×IL + 0.45×DEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="10" t="inlineStr">
+        <is>
+          <t>Venom Repeater</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F52" s="10" t="n">
+        <v>105</v>
+      </c>
+      <c r="G52" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H52" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Each hit Power = 5 + 0.12×IL + 0.20×DEX; 2+ HP hits apply Poison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t>Flame Projector</t>
+        </is>
+      </c>
+      <c r="B53" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F53" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="G53" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H53" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Fire Power = 14 + 0.32×IL + 0.30×INT per tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>Cryo Emitter</t>
+        </is>
+      </c>
+      <c r="B54" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C54" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F54" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="G54" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H54" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Ice Power = 15 + 0.35×IL + 0.30×INT; center receives 50 RT Delay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Corrosion Sprayer</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F55" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="G55" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H55" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Poison Power = 10 + 0.25×IL + 0.20×INT; Defense −10% for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
+        <is>
+          <t>Rupture Disc</t>
+        </is>
+      </c>
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="G56" s="10" t="n">
+        <v>75</v>
+      </c>
+      <c r="H56" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Physical Power = 16 + 0.35×IL + 0.45×DEX; first target gains Bleed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>Emergency Medium Healing Potion</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>Quick</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="G57" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="H57" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="I57" s="11" t="inlineStr">
+        <is>
+          <t>Restore 50% target Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>Regeneration Injector</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G58" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="H58" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="I58" s="11" t="inlineStr">
+        <is>
+          <t>Restore 8% Max HP at 0, 400, 800, 1200, and 1600 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>Medium Healing Potion</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="H59" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="I59" s="11" t="inlineStr">
+        <is>
+          <t>Restore 50% target Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Trauma Kit</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>Uncommon</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="G60" s="11" t="n">
+        <v>105</v>
+      </c>
+      <c r="H60" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="I60" s="11" t="inlineStr">
+        <is>
+          <t>Restore 25% Max HP and remove Bleed, Raptured, and Wounded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="12" t="inlineStr">
+        <is>
+          <t>Emergency Greater Ether</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C61" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D61" s="12" t="inlineStr">
+        <is>
+          <t>Quick</t>
+        </is>
+      </c>
+      <c r="E61" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I61" s="12" t="inlineStr">
+        <is>
+          <t>Restore 50% target Max MP, minimum 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="12" t="inlineStr">
+        <is>
+          <t>Emergency Large Healing Potion</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C62" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D62" s="12" t="inlineStr">
+        <is>
+          <t>Quick</t>
+        </is>
+      </c>
+      <c r="E62" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I62" s="12" t="inlineStr">
+        <is>
+          <t>Restore 75% target Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Snare Dispenser</t>
+        </is>
+      </c>
+      <c r="B63" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C63" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D63" s="12" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E63" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I63" s="12" t="inlineStr">
+        <is>
+          <t>First enemy is Pinned for 1000 CT and movement ends.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="12" t="inlineStr">
+        <is>
+          <t>Mine Dispenser</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C64" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D64" s="12" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E64" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I64" s="12" t="inlineStr">
+        <is>
+          <t>Trigger Power = 20 + 0.45×IL + 0.40×DEX plus 30 RT Delay.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
+        <is>
+          <t>Decoy Totem</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C65" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I65" s="12" t="inlineStr">
+        <is>
+          <t>High-priority AI target with HP = 12 + 0.40×IL + 0.25×VIT for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>Greater Ether Cell</t>
+        </is>
+      </c>
+      <c r="B66" s="12" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C66" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D66" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E66" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I66" s="12" t="inlineStr">
+        <is>
+          <t>Restore 50% target Max MP, minimum 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Purification Device</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C67" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I67" s="12" t="inlineStr">
+        <is>
+          <t>Remove one selected dispellable debuff from every allied target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Emergency Triage Pack</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C68" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D68" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I68" s="12" t="inlineStr">
+        <is>
+          <t>Restore 40% Max HP; if target was below 20%, grant Shield = 10% Max HP for 500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="12" t="inlineStr">
+        <is>
+          <t>Dazzle Beacon</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C69" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I69" s="12" t="inlineStr">
+        <is>
+          <t>Apply Blind for 800 CT at creation and again after 600 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="12" t="inlineStr">
+        <is>
+          <t>Smoke Generator</t>
+        </is>
+      </c>
+      <c r="B70" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C70" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D70" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E70" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H70" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I70" s="12" t="inlineStr">
+        <is>
+          <t>Create Smoke while active, maximum 1600 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="12" t="inlineStr">
+        <is>
+          <t>Confusion Projector</t>
+        </is>
+      </c>
+      <c r="B71" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C71" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D71" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I71" s="12" t="inlineStr">
+        <is>
+          <t>Apply Confuse for 2 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="12" t="inlineStr">
+        <is>
+          <t>Taunt Beacon</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C72" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E72" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I72" s="12" t="inlineStr">
+        <is>
+          <t>Enemies increase target priority toward beacon for 1000 CT when legal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>Fortification Projector</t>
+        </is>
+      </c>
+      <c r="B73" s="12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C73" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E73" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I73" s="12" t="inlineStr">
+        <is>
+          <t>Allies gain VIT +12% for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="12" t="inlineStr">
+        <is>
+          <t>Elemental Ward</t>
+        </is>
+      </c>
+      <c r="B74" s="12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C74" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D74" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E74" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H74" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I74" s="12" t="inlineStr">
+        <is>
+          <t>Choose element; incoming direct damage of that tag ×0.75 for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="12" t="inlineStr">
+        <is>
+          <t>Blessing Projector</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C75" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E75" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I75" s="12" t="inlineStr">
+        <is>
+          <t>Extend one dispellable positive effect by 500 CT, up to its authored maximum extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Fog Machine</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C76" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D76" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E76" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H76" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I76" s="12" t="inlineStr">
+        <is>
+          <t>Create Smoke aura for up to 1600 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="12" t="inlineStr">
+        <is>
+          <t>Icebreaker Array</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C77" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D77" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E77" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H77" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I77" s="12" t="inlineStr">
+        <is>
+          <t>Convert Ice to Shallow Water and end voluntary sliding effects on affected tiles.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Hologram Projector</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C78" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D78" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E78" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H78" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I78" s="12" t="inlineStr">
+        <is>
+          <t>Project false unit presence for AI/visibility rules for 800 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="12" t="inlineStr">
+        <is>
+          <t>Scout Drone</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C79" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D79" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E79" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I79" s="12" t="inlineStr">
+        <is>
+          <t>Reveal hidden units, traps, and objects for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="12" t="inlineStr">
+        <is>
+          <t>Phase Translocator</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C80" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E80" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H80" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I80" s="12" t="inlineStr">
+        <is>
+          <t>Teleport to a legal empty tile.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="12" t="inlineStr">
+        <is>
+          <t>Recruitment Beacon</t>
+        </is>
+      </c>
+      <c r="B81" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C81" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E81" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="12" t="n">
+        <v>135</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I81" s="12" t="inlineStr">
+        <is>
+          <t>Recruitable enemies in area reveal requirements and gain +10 percentage points to next attempt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="12" t="inlineStr">
+        <is>
+          <t>Void Shard Array</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C82" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E82" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H82" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I82" s="12" t="inlineStr">
+        <is>
+          <t>Dark Power = 30 + 0.60×IL + 0.40×INT; user pays 8% Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>Breaching Drill</t>
+        </is>
+      </c>
+      <c r="B83" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C83" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E83" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F83" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I83" s="12" t="inlineStr">
+        <is>
+          <t>Object Power = 55 + 1.00×IL + 0.70×STR; unit Power = 45% of object value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="12" t="inlineStr">
+        <is>
+          <t>Nullifier Wand</t>
+        </is>
+      </c>
+      <c r="B84" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D84" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I84" s="12" t="inlineStr">
+        <is>
+          <t>Apply Silence for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Augment Scrambler</t>
+        </is>
+      </c>
+      <c r="B85" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E85" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I85" s="12" t="inlineStr">
+        <is>
+          <t>Apply Mute for 2000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="12" t="inlineStr">
+        <is>
+          <t>Fear Projector</t>
+        </is>
+      </c>
+      <c r="B86" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D86" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E86" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I86" s="12" t="inlineStr">
+        <is>
+          <t>Apply authored Fear movement restriction for 2 turns.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="12" t="inlineStr">
+        <is>
+          <t>Barrier Generator</t>
+        </is>
+      </c>
+      <c r="B87" s="12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E87" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F87" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I87" s="12" t="inlineStr">
+        <is>
+          <t>Allies gain Shield = 8 + 0.12×IL + 8% Max HP for 800 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>War Cry Horn</t>
+        </is>
+      </c>
+      <c r="B88" s="12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I88" s="12" t="inlineStr">
+        <is>
+          <t>Allies gain direct final damage +12% for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="12" t="inlineStr">
+        <is>
+          <t>Command Relay</t>
+        </is>
+      </c>
+      <c r="B89" s="12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D89" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I89" s="12" t="inlineStr">
+        <is>
+          <t>Movement Range +1 and next non-Item action RT ×0.80 before end of next turn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="12" t="inlineStr">
+        <is>
+          <t>Barricade Projector</t>
+        </is>
+      </c>
+      <c r="B90" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C90" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D90" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I90" s="12" t="inlineStr">
+        <is>
+          <t>Create barricade HP = 20 + 0.60×IL + 0.50×VIT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="12" t="inlineStr">
+        <is>
+          <t>Stasis Trap Emitter</t>
+        </is>
+      </c>
+      <c r="B91" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C91" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D91" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I91" s="12" t="inlineStr">
+        <is>
+          <t>Apply 100 + 0.35×IL RT Delay to enemies in area.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="12" t="inlineStr">
+        <is>
+          <t>Chronometer</t>
+        </is>
+      </c>
+      <c r="B92" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C92" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D92" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I92" s="12" t="inlineStr">
+        <is>
+          <t>Reduce remaining RT by round(100 + 0.30×IL), minimum 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>Charge Relay</t>
+        </is>
+      </c>
+      <c r="B93" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D93" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I93" s="12" t="inlineStr">
+        <is>
+          <t>Transfer 1 charge from user’s Item to the same Item equipped by target.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="12" t="inlineStr">
+        <is>
+          <t>Large Healing Potion</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D94" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I94" s="12" t="inlineStr">
+        <is>
+          <t>Restore 75% target Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
+        <is>
+          <t>Revival Injector</t>
+        </is>
+      </c>
+      <c r="B95" s="12" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C95" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D95" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="I95" s="12" t="inlineStr">
+        <is>
+          <t>Revive at 25% Max HP with 300 remaining RT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="12" t="inlineStr">
+        <is>
+          <t>Arc Coil</t>
+        </is>
+      </c>
+      <c r="B96" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C96" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D96" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I96" s="12" t="inlineStr">
+        <is>
+          <t>First target Power = 22 + 0.45×IL + 0.35×DEX; jumps at 70% and 50%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="12" t="inlineStr">
+        <is>
+          <t>Sanctifier Relic</t>
+        </is>
+      </c>
+      <c r="B97" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C97" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I97" s="12" t="inlineStr">
+        <is>
+          <t>Holy Power = 18 + 0.40×IL + 0.35×INT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>Thermite Projector</t>
+        </is>
+      </c>
+      <c r="B98" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C98" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E98" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F98" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H98" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I98" s="12" t="inlineStr">
+        <is>
+          <t>At 0, 400, 800, 1200 CT: Fire Power = 10 + 0.20×IL + 0.20×INT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="12" t="inlineStr">
+        <is>
+          <t>Kinetic Ram</t>
+        </is>
+      </c>
+      <c r="B99" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C99" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D99" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I99" s="12" t="inlineStr">
+        <is>
+          <t>Push Force = 2 + floor(IL/80) + floor(STR/100); collision multiplier ×1.25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="12" t="inlineStr">
+        <is>
+          <t>Stasis Projector</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C100" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I100" s="12" t="inlineStr">
+        <is>
+          <t>RT Delay = round(100 + 0.40×IL) before resistance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="12" t="inlineStr">
+        <is>
+          <t>Cryogenic Field Unit</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C101" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D101" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I101" s="12" t="inlineStr">
+        <is>
+          <t>Convert compatible Water to Ice; other tiles gain +1 Move Cost for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="12" t="inlineStr">
+        <is>
+          <t>Terrain Compactor</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I102" s="12" t="inlineStr">
+        <is>
+          <t>Convert Mud/Swamp to Rocky or stabilize Cracked Ground.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Gale Engine</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C103" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I103" s="12" t="inlineStr">
+        <is>
+          <t>Disperse light zones and push units with Force 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="12" t="inlineStr">
+        <is>
+          <t>Barrier Pylon</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C104" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I104" s="12" t="inlineStr">
+        <is>
+          <t>Barrier HP = 25 + 0.75×IL + 0.60×VIT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="12" t="inlineStr">
+        <is>
+          <t>Elemental Ward Totem</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C105" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I105" s="12" t="inlineStr">
+        <is>
+          <t>Choose element; allies take ×0.80 direct damage from that tag.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="12" t="inlineStr">
+        <is>
+          <t>Poison Cloud Vent</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C106" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I106" s="12" t="inlineStr">
+        <is>
+          <t>Create Poison Cloud pulses at 400, 800, and 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="12" t="inlineStr">
+        <is>
+          <t>Exchange Device</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C107" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I107" s="12" t="inlineStr">
+        <is>
+          <t>Swap positions; enemy may resist through approved resistance comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>Object Recall Device</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C108" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>145</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I108" s="12" t="inlineStr">
+        <is>
+          <t>Relocate owned deployable to legal empty tile; remaining duration unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="12" t="inlineStr">
+        <is>
+          <t>Shadow Lantern</t>
+        </is>
+      </c>
+      <c r="B109" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C109" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="I109" s="12" t="inlineStr">
+        <is>
+          <t>Dark Power = 16 + 0.35×IL + 0.30×INT; restore 20% of final HP damage, capped at 15% Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="12" t="inlineStr">
+        <is>
+          <t>Passive Breaker Seal</t>
+        </is>
+      </c>
+      <c r="B110" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C110" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D110" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="I110" s="12" t="inlineStr">
+        <is>
+          <t>Apply Break for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="12" t="inlineStr">
+        <is>
+          <t>Guardian Standard</t>
+        </is>
+      </c>
+      <c r="B111" s="12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D111" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>155</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="I111" s="12" t="inlineStr">
+        <is>
+          <t>Allies gain +5 Guard percentage points and Stability +1 while in aura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="12" t="inlineStr">
+        <is>
+          <t>Tesla Pylon</t>
+        </is>
+      </c>
+      <c r="B112" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C112" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D112" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E112" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H112" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="I112" s="12" t="inlineStr">
+        <is>
+          <t>At 500 and 1000 CT, strike nearest enemy for 20 + 0.45×IL + 0.35×INT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>Gravity Anchor</t>
+        </is>
+      </c>
+      <c r="B113" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C113" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D113" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E113" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H113" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="I113" s="12" t="inlineStr">
+        <is>
+          <t>Units gain Stability +2 and Movement Range −1 for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="12" t="inlineStr">
+        <is>
+          <t>Excavation Drill</t>
+        </is>
+      </c>
+      <c r="B114" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C114" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E114" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H114" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="I114" s="12" t="inlineStr">
+        <is>
+          <t>Reduce approved terrain elevation by 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>Portal Stabilizer</t>
+        </is>
+      </c>
+      <c r="B115" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D115" s="12" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="E115" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="12" t="n">
+        <v>160</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="H115" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="I115" s="12" t="inlineStr">
+        <is>
+          <t>Fix one random portal to a previewed legal destination for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>Hardlight Wall</t>
+        </is>
+      </c>
+      <c r="B116" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D116" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E116" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H116" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I116" s="12" t="inlineStr">
+        <is>
+          <t>Create three segments, each HP = 15 + 0.45×IL + 0.35×VIT for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>Survey Drone</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D117" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H117" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I117" s="12" t="inlineStr">
+        <is>
+          <t>Reveal and relocate up to 2 tiles every 400 CT for 1600 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>Tactical Recorder</t>
+        </is>
+      </c>
+      <c r="B118" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E118" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="12" t="n">
+        <v>180</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H118" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I118" s="12" t="inlineStr">
+        <is>
+          <t>For current turn, rank top three deterministic action outcomes without changing legality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>Suppression Field</t>
+        </is>
+      </c>
+      <c r="B119" s="12" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E119" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H119" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I119" s="12" t="inlineStr">
+        <is>
+          <t>Enemy voluntary actions in zone add 30 RT for 1200 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>Rally Array</t>
+        </is>
+      </c>
+      <c r="B120" s="12" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E120" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H120" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I120" s="12" t="inlineStr">
+        <is>
+          <t>Allies gain STR, INT, and VIT +10% for 1000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>Sun Beacon</t>
+        </is>
+      </c>
+      <c r="B121" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H121" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I121" s="12" t="inlineStr">
+        <is>
+          <t>Set Clear/Sunny for 1800 CT and end ordinary Rain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>Sentry Turret</t>
+        </is>
+      </c>
+      <c r="B122" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E122" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H122" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I122" s="12" t="inlineStr">
+        <is>
+          <t>HP = 22 + 0.65×IL + 0.40×VIT; 3 shots at 500 CT intervals for 14 + 0.32×IL + 0.25×DEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>Healing Beacon</t>
+        </is>
+      </c>
+      <c r="B123" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E123" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H123" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I123" s="12" t="inlineStr">
+        <is>
+          <t>Four pulses every 400 CT heal allies for 5% Max HP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>Countermeasure Turret</t>
+        </is>
+      </c>
+      <c r="B124" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E124" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H124" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I124" s="12" t="inlineStr">
+        <is>
+          <t>Intercept first three hostile projectiles entering aura; one interception per resolution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>Mender Drone</t>
+        </is>
+      </c>
+      <c r="B125" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E125" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="12" t="n">
+        <v>185</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H125" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I125" s="12" t="inlineStr">
+        <is>
+          <t>At 500 and 1000 CT, heal lowest-HP ally in Range 3 for 10 + 0.20×IL + 0.25×INT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>Road Fabricator</t>
+        </is>
+      </c>
+      <c r="B126" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E126" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H126" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I126" s="12" t="inlineStr">
+        <is>
+          <t>Create temporary road state reducing positive movement penalties by 1 for 2000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>Weather Stabilizer</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E127" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H127" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I127" s="12" t="inlineStr">
+        <is>
+          <t>Suppress non-locked weather modifiers locally for 1600 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>Supply Station</t>
+        </is>
+      </c>
+      <c r="B128" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E128" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H128" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I128" s="12" t="inlineStr">
+        <is>
+          <t>Three supplies; each allied unit may Interact once to restore 1 Item charge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>Weather Stabilizer Totem</t>
+        </is>
+      </c>
+      <c r="B129" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H129" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I129" s="12" t="inlineStr">
+        <is>
+          <t>Suppress local non-locked weather modifiers for 1600 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>Gravity Pylon</t>
+        </is>
+      </c>
+      <c r="B130" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E130" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="12" t="n">
+        <v>190</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H130" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I130" s="12" t="inlineStr">
+        <is>
+          <t>Units in aura gain Stability +2 and cannot teleport, blink, or swap.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>Rain Beacon</t>
+        </is>
+      </c>
+      <c r="B131" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H131" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I131" s="12" t="inlineStr">
+        <is>
+          <t>Set Rain for 2000 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>Rescue Beacon</t>
+        </is>
+      </c>
+      <c r="B132" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E132" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H132" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I132" s="12" t="inlineStr">
+        <is>
+          <t>First allied KO is relocated adjacent and revived at 15% Max HP with 400 RT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>Loadout Replicator</t>
+        </is>
+      </c>
+      <c r="B133" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E133" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H133" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I133" s="12" t="inlineStr">
+        <is>
+          <t>Copy one charge and effect access from an ally’s equipped Item for this battle; cannot copy another Replicator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="12" t="inlineStr">
+        <is>
+          <t>Storm Core</t>
+        </is>
+      </c>
+      <c r="B134" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E134" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="12" t="n">
+        <v>205</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H134" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I134" s="12" t="inlineStr">
+        <is>
+          <t>Set Thunderstorm for 1500 CT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>Bridge Projector</t>
+        </is>
+      </c>
+      <c r="B135" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E135" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H135" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I135" s="12" t="inlineStr">
+        <is>
+          <t>Create energy bridge for 2000 CT; cannot expire while occupied.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="12" t="inlineStr">
+        <is>
+          <t>Emergency Extraction Beacon</t>
+        </is>
+      </c>
+      <c r="B136" s="12" t="inlineStr">
+        <is>
+          <t>Utility</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E136" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="12" t="n">
+        <v>210</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H136" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I136" s="12" t="inlineStr">
+        <is>
+          <t>After 500 CT, qualifying allied units in aura withdraw safely if scenario permits extraction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>Meteor Marker</t>
+        </is>
+      </c>
+      <c r="B137" s="12" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E137" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H137" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I137" s="12" t="inlineStr">
+        <is>
+          <t>After 300 CT: Fire Power = 60 + 1.00×IL + 0.80×INT; rings deal 100%/65%/35%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>Terraforming Array</t>
+        </is>
+      </c>
+      <c r="B138" s="12" t="inlineStr">
+        <is>
+          <t>Environment</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E138" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H138" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I138" s="12" t="inlineStr">
+        <is>
+          <t>Choose legal Rocky, Mud, Shallow Water, or Sand transformation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>Portable Ballista</t>
+        </is>
+      </c>
+      <c r="B139" s="12" t="inlineStr">
+        <is>
+          <t>Deployable</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>Rare</t>
+        </is>
+      </c>
+      <c r="D139" s="12" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E139" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="12" t="n">
+        <v>220</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="H139" s="12" t="n">
+        <v>320</v>
+      </c>
+      <c r="I139" s="12" t="inlineStr">
+        <is>
+          <t>Two shots, Range 3–7, Power = 50 + 0.90×IL + 0.60×DEX.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="inlineStr">
+        <is>
+          <t>Resuscitation Device</t>
+        </is>
+      </c>
+      <c r="B140" s="13" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C140" s="13" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D140" s="13" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="13" t="n">
+        <v>185</v>
+      </c>
+      <c r="G140" s="13" t="n">
+        <v>480</v>
+      </c>
+      <c r="H140" s="13" t="n">
+        <v>480</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>Revive at 40% Max HP with 350 remaining RT and remove one wound-family status.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="13" t="inlineStr">
+        <is>
+          <t>Field Restorative Array</t>
+        </is>
+      </c>
+      <c r="B141" s="13" t="inlineStr">
+        <is>
+          <t>Recovery</t>
+        </is>
+      </c>
+      <c r="C141" s="13" t="inlineStr">
+        <is>
+          <t>Epic</t>
+        </is>
+      </c>
+      <c r="D141" s="13" t="inlineStr">
+        <is>
+          <t>Battlefield</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="13" t="n">
+        <v>190</v>
+      </c>
+      <c r="G141" s="13" t="n">
+        <v>480</v>
+      </c>
+      <c r="H141" s="13" t="n">
+        <v>480</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>Restore 20% Max HP and 15% Max MP to each ally in area.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="85" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>Rule</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>Principle</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>Facilities cost gold only. Materials are exclusively for equipment upgrades at the Blacksmith. Clean separation: gold → infrastructure, materials → gear.</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>Gold Cost Formula</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>round(Base × (1 + Level² / Scale)). Quadratic curve — early levels cheap, late levels expensive. Each facility has its own Base and Scale.</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>Guild Hall Gatekeeper</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Guild Hall level gates other facility max levels. A facility cannot exceed the Guild Hall level that unlocked it. Guild Hall must be upgraded first.</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>No Material Cost</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Facility upgrades require zero materials. T5 Ethereal Essence is reserved for blacksmith item upgrades (L81-99 equipment). Prevents cross-contamination between building infrastructure and upgrading gear.</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Design</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Total Investment</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>62,008g across all 9 facilities. Free player maxes 6/9 (Guild Hall, Tavern, Blacksmith, Merchant, Quest Board, Workshop). Boosted player (+25%) maxes 9/9.</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Locked — verified by simulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Guild Hall</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 10. Base = 250, Scale = 15. Total cost: 8,919g. Unlock: Starting facility.</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Guild Hall</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Gatekeeper — unlocks other facilities. Each level: +1 quest board slot, +1 dispatch slot (up to base max). Guild Hall level gates other facility max levels.</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Guild Hall</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Unlock Schedule</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>L1: Tavern. L2: Blacksmith, Merchant. L3: Quest Board. L4: Workshop. L5: Training Ground. L6: Library. L7: Trophy Hall.</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Tavern</t>
+        </is>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C10" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 10. Base = 200, Scale = 18. Total cost: 6,277g. Unlock: Guild Hall L1.</t>
+        </is>
+      </c>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Tavern</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Recruitment pool size, quality tiers, race variety. Each level: +1 recruit pool size. L5: Quality recruits available. L8: Elite recruits available.</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 10. Base = 300, Scale = 12. Total cost: 12,625g. Unlock: Guild Hall L2.</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Equipment upgrades. Max upgradeable item level = Level × 10 (L1=10, L5=50, L10=99). Rarity recipe unlocks per level. Material conversion unlocked at L3.</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Rarity Unlocks</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>L1: Common/Uncommon upgrades. L3: Rare upgrades + Material Conversion. L5: Epic upgrades. L7: Legendary upgrades. L9: Mythic upgrades.</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 10. Base = 200, Scale = 18. Total cost: 6,277g. Unlock: Guild Hall L2.</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Shop stock and quality. Each level: +1 stock slot. L5: Uncommon items in stock. L8: Rare items in stock. Stock refreshes after N battles (refresh rate pending).</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Quest Board</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 10. Base = 180, Scale = 20. Total cost: 5,265g. Unlock: Guild Hall L3.</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Quest Board</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Quest availability and difficulty. Each level: +1 available quest. L5: Elite quests. L8: Boss quests.</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 10. Base = 150, Scale = 22. Total cost: 4,123g. Unlock: Guild Hall L4.</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Consumable management. Each level: +1 consumable slot access (base 3, max 6). Access to higher-tier consumable purchases. Consumable stock rotation.</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Training Ground</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 10. Base = 220, Scale = 16. Total cost: 7,495g. Unlock: Guild Hall L5.</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Training Ground</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Passive XP for benched units. Each level: benched XP bonus +2% (L1: 67%, L10: 85%). Unlocks training battles and class/skill preview.</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 10. Base = 200, Scale = 18. Total cost: 6,277g. Unlock: Guild Hall L6.</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Skill Card and Augment Card management. Each level: +1 card storage. Access to card merchants (buy/trade). Card research (slow free acquisition).</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Trophy Hall</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Parameters</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Max Level 5. Base = 400, Scale = 8. Total cost: 4,750g. Unlock: Guild Hall L7.</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>Trophy Hall</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Function</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>HQ decoration. Displays trophies and collections. Functional bonuses from completed sets (e.g., +5% dispatch reward, +1 recruit pool). Social/flex value.</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>Guild Hall</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>L1:267 L2:317 L3:400 L4:517 L5:667 L6:850 L7:1067 L8:1317 L9:1600 L10:1917. Total: 8,919g.</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Tavern</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>L1:211 L2:244 L3:300 L4:378 L5:478 L6:600 L7:744 L8:911 L9:1100 L10:1311. Total: 6,277g.</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>Blacksmith</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>L1:325 L2:400 L3:525 L4:700 L5:925 L6:1200 L7:1525 L8:1900 L9:2325 L10:2800. Total: 12,625g.</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Merchant</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>L1:211 L2:244 L3:300 L4:378 L5:478 L6:600 L7:744 L8:911 L9:1100 L10:1311. Total: 6,277g.</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Quest Board</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>L1:189 L2:216 L3:261 L4:324 L5:405 L6:504 L7:621 L8:756 L9:909 L10:1080. Total: 5,265g.</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>L1:157 L2:178 L3:212 L4:259 L5:320 L6:395 L7:483 L8:586 L9:702 L10:832. Total: 4,123g.</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Training Ground</t>
+        </is>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>L1:234 L2:275 L3:344 L4:440 L5:564 L6:715 L7:894 L8:1100 L9:1334 L10:1595. Total: 7,495g.</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Library</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>L1:211 L2:244 L3:300 L4:378 L5:478 L6:600 L7:744 L8:911 L9:1100 L10:1311. Total: 6,277g.</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Cost Table</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Trophy Hall</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>L1:450 L2:600 L3:850 L4:1200 L5:1650. Total: 4,750g.</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Free Player (L1→L99)</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="inlineStr">
+        <is>
+          <t>Maxes 6/9 facilities: Guild Hall L10, Tavern L10, Blacksmith L10, Merchant L10, Quest Board L10, Workshop L10. Training Ground L7, Library L3, Trophy Hall L0. Budget: 47,962g.</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>Boosted Player (+25%)</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Maxes 9/9 facilities with ~29,900g surplus. Budget: 91,902g.</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>Expense Ratio</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Necessities (73%) + Facilities (35%) = 108% total. Free player deficit ~14,000g. Creates the intended 'can't do everything' pressure on luxury facilities.</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Simulation Benchmarks</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>Material Wall</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Equipment upgrades break at 13 items (T3/T4 exhaustion). 10 upgrades = 89% budget (comfortable). 12 = 98% (razor thin). 15 = deficit requiring ~27 targeted battles. Documented as intentional soft wall.</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="inlineStr">
+        <is>
+          <t>Verified — per Simulator agent</t>
         </is>
       </c>
     </row>
